--- a/Experiencia SGA-GEOBIOTA.xlsx
+++ b/Experiencia SGA-GEOBIOTA.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaExperiencia" displayName="TablaExperiencia" ref="A1:N309" headerRowCount="1">
-  <autoFilter ref="A1:N309"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaExperiencia" displayName="TablaExperiencia" ref="A1:N310" headerRowCount="1">
+  <autoFilter ref="A1:N310"/>
   <tableColumns count="14">
     <tableColumn id="1" name="n"/>
     <tableColumn id="2" name="nombre_proyecto"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N309"/>
+  <dimension ref="A1:N310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Río Seco S.A.</t>
+          <t>Nueva Energía de Chile S.A.</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -20458,104 +20458,104 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Modificación de Proyecto Gasoducto GasAndes, Extensión a la VI Región, Ruta San Vicente- Caletones</t>
+          <t>Modificación Terminal GNL Quintero: Construcción Planta Desalinizadora Aguas El Bato y Extensión Emisario Agua de Mar</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>580643</t>
+          <t>2168836458</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=580643&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2168836458&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Interregional</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>0,001</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>26/01/2005</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Aprobado</t>
+          <t>En Admisión</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Declaración de Impacto Ambiental</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>Gasoductos</t>
+          <t>Estudio de Impacto Ambiental</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Gasoducto GasAndes S.A.</t>
+          <t>GNL QUINTERO S.A.</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>Geobiota</t>
+          <t>SGA</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Félix Hidalgo Reyes</t>
+          <t>Ricardo Jorge Gonzalorena Vallejos</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>El Proyecto “Modificación Terminal GNL Quintero: Construcción Planta Desalinizadora Aguas El Bato y Extensión Emisario Agua de Mar” (el Proyecto) corresponde a una modificación del Terminal de Gas Natural Licuado de GNL Quintero (Terminal GNLQ), aprobado ambientalmente mediante Res Ex. N°323/2005 y sus modificaciones. Este Proyecto se emplazará en la bahía de Quintero, en las comunas de Quintero y Puchuncaví, provincia y región de Valparaíso, y consiste en la construcción y operación de una planta desalinizadora de agua de mar ubicada íntegramente al interior del Terminal de GNLQ. Además, considera la modificación del emisario submarino y su difusor, así como la optimización del sistema de captación de agua de mar, los cuales se encuentran actualmente en operación. El objetivo será la producción de 2.000 l/s de agua desalinizada, lo cual será implementado en dos subfases: una capacidad inicial de producción hasta 1.000 l/s (subfase I), que se incrementará hasta 2.000 l/s (subfase II). Para lograr la máxima producción de agua desalinizada, se requerirá un caudal nominal de 16.850 m3/h de agua de mar. Respecto de la captación de agua de mar, se hace presente que el Terminal ya cuenta con infraestructura de captación, la cual actualmente es utilizada para el proceso de regasificación de GNL. Por esta razón, no se construirá una nueva toma de agua de mar y se mantendrán los límites de caudal aprobados, considerando como parte del Proyecto incorporar una cortina de burbujas en la captación y la instalación de una bomba de agua en la estación de bombeo existente. De este modo, el agua de mar para la planta desalinizadora se derivará desde el sistema de retorno de agua del proceso de regasificación de GNL, para lo cual se construirá una nueva sentina dentro del Terminal GNLQ que permitirá impulsar el agua de mar desde la descarga de los ORV hacia la planta. Además, se instalará un sistema de derivación (by-pass) de los ORV, que permitirá asegurar el caudal necesario para la desalinización, de manera independiente del flujo requerido por el proceso de regasificación. Respecto de la planta desalinizadora, esta considera un pretratamiento, compuesto por una serie de sistemas de filtración y de separación (flotación por aire disuelto, trampa de sólidos y ultrafiltración), seguido de la osmosis inversa para la desalinización del agua de mar y finalmente un post-tratamiento, donde se realizará un proceso de remineralización del agua. El agua de producto obtenida será almacenada en un estanque desde donde será conducida hasta un punto de entrega (dentro del Terminal GNLQ). En dicho punto se podrán conectar eventualmente empresas sanitarias con red existente en la zona u otros usuarios que deberán incluir una solución de transporte, por lo que su distribución no forma parte del presente Proyecto. La salmuera generada en los procesos de la planta desalinizadora será descargada al mar por el emisario submarino existente en el Terminal GNLQ, el cual será modificado como parte del presente Proyecto, considerando su extensión en 600 m de longitud. Como parte de esta extensión se considera la instalación de un nuevo difusor de descarga, compuesto por un total de 36 válvulas de tipo duckbill (24 en la subfase I y 12 en la subfase II), las cuales permitirán mejorar la dispersión y dilución de la salmuera. Cabe indicar que se mantendrán los límites aprobados de caudal de descarga del Terminal GNLQ. No obstante, la salmuera presentará una composición distinta a la de la operación actual, con mayor salinidad y otros compuestos producto del proceso de desalinización. Respecto de lo anterior, se dará cumplimiento al D.S. N°90 del MINSAL y la tabla específica que regula descargas más allá de la Zona de Protección Litoral. Por otro lado, para el abastecimiento eléctrico, el Proyecto contempla la construcción de una Línea de Alta Tensión soterrada de 110 kV de 492 metros de longitud, que se extenderá desde la Subestación GNL Quintero existente hasta la nueva Sala Eléctrica proyectada al interior del mismo Terminal. Objetivo El Proyecto tiene como objetivo principal la construcción y operación de una planta desalinizadora dentro del Terminal de GNL Quintero, destinada a producir hasta 2.000 l/s de agua desalinizada y remineralizada en dos subfases de igual capacidad (1.000 l/s en la subfase I y 1.000 l/s adicionales en la subfase II).</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Estanques de Combustible  Fase II</t>
+          <t>Modificación de Proyecto Gasoducto GasAndes, Extensión a la VI Región, Ruta San Vicente- Caletones</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>622276</t>
+          <t>580643</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=622276&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=580643&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Interregional</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>1,500</t>
+          <t>0,001</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>11/03/2005</t>
+          <t>26/01/2005</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -20570,12 +20570,12 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Producción, almacenamiento, disposición o reutilización o transporte por medios terrestres de sustancias inflamables, (sustancias señaladas en las clases 3 y 4 de la NCh. 2120/Of. 89)</t>
+          <t>Gasoductos</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>SQM Industrial S.A.</t>
+          <t>Gasoducto GasAndes S.A.</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -20592,37 +20592,37 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Proyecto de Prospección Minera, Sitio Río Figueroa, III Región</t>
+          <t>Estanques de Combustible  Fase II</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>947358</t>
+          <t>622276</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=947358&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=622276&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Tercera</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>1,500</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>26/07/2005</t>
+          <t>11/03/2005</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -20637,12 +20637,12 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Proyecto de desarrollo minero sobre 5000 tons/mens</t>
+          <t>Producción, almacenamiento, disposición o reutilización o transporte por medios terrestres de sustancias inflamables, (sustancias señaladas en las clases 3 y 4 de la NCh. 2120/Of. 89)</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Minera Metallica Resources Chile Limitada</t>
+          <t>SQM Industrial S.A.</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -20659,22 +20659,22 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Proyecto de Prospección Minera Vicuña, Sector Los Helados, III Región</t>
+          <t>Proyecto de Prospección Minera, Sitio Río Figueroa, III Región</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>1241306</t>
+          <t>947358</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1241306&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=947358&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -20684,12 +20684,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>0,377</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>25/01/2006</t>
+          <t>26/07/2005</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -20709,59 +20709,64 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Minera Frontera del Oro SpA</t>
+          <t>Minera Metallica Resources Chile Limitada</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>Geobiota</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Félix Hidalgo Reyes</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Soronal</t>
+          <t>Proyecto de Prospección Minera Vicuña, Sector Los Helados, III Región</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>1314604</t>
+          <t>1241306</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1314604&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1241306&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Primera</t>
+          <t>Tercera</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>231,000</t>
+          <t>0,377</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>08/02/2006</t>
+          <t>25/01/2006</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Desistido</t>
+          <t>Aprobado</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Estudio de Impacto Ambiental</t>
+          <t>Declaración de Impacto Ambiental</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -20771,116 +20776,116 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>SQM Industrial S.A.</t>
+          <t>Minera Frontera del Oro SpA</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>Geobiota</t>
-        </is>
-      </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>1.1 Antecedentes generales El proyecto "Soronal" se emplaza en la comuna de Pozo Almonte, I Región de Tarapacá, su titular es SQM S.A. y contempla una inversión de US$ 231.000.000, la que se haría gradualmente durante la vida útil de 30 años del proyecto. El principal objetivo del proyecto es aumentar la capacidad de actual de yodo en 6.000 ton/año, alcanzando una capacidad de 10.500 ton/año1, en las instalaciones del complejo industrial Operación Nueva Victoria y una capacidad de producción de 900.000 ton/año de nitrato de sodio y/o nitrato de potasio en las instalaciones industriales de Sur Viejo. A fin de satisfacer este objetivo, el proyecto contempla: o Incorporar 248,8 km2 de nuevas áreas de mina, con una tasa de extracción máxima de caliche de 35.000.000 ton/año 2; o Aumentar la capacidad de producción de yoduro en un monto equivalente a 7.000 ton/año de yodo; 3 o Aumentar la capacidad productiva de la planta de yodo en 6.000 ton/año; o Aumentar área de evaporación solar para producción de sales de nitrato; o Incorporar una nueva planta de proceso para la producción de nitrato de sodio y/o nitrato de potasio (Planta de Nitratos); o Habilitar y ejercer el total de los derechos de agua de 11 pozos, localizados al oeste del Salar de Bellavista (6 pozos), al este del Salar de Bellavista (1pozo), en el Salar de Pintado (1 pozo) y en el Salar de Llamara (3 pozos), y ejercer el total de los derechos de agua constituidos en 4 pozos actualmente habilitados en el Salar de Llamara. La ejecución de este proyecto obedece a un incremento observable en la demanda de yodo y de nitrato a nivel mundial. Lo que genera la necesidad de contar con instalaciones que permitan satisfacer dicha demanda en los próximos años. El proyecto contempla planes de seguimiento ambiental, planes de contingencias y una serie de medidas especialmente diseñadas para fortalecer una operación ambientalmente segura. 1.2 Localización geográfica y administrativa El proyecto se localiza en la Primera Región de Tarapacá, provincia de Iquique, comuna de Pozo Almonte. Específicamente, a unos 145 km al sureste de la ciudad de Iquique y a unos 25 km al sur de Pozo Almonte, en un área circunscrita por las coordenadas N: 7.657.992 y N: 7.736.401 y las coordenadas E: 409.150 y E: 450.345. 1.3 Componentes del proyecto y superficie involucrada A continuación se presenta una breve descripción de las diferentes obras que forman parte del proyecto. a. Areas de mina (AM): Corresponden a quince nuevas áreas de explotación de caliche, las que involucran una superficie total de 248,8 km2. Estas áreas se agrupan en tres grandes sectores, a saber: o Sector Coruña: Incluye el área de mina AM 1 o Sector Soronal: Incluye las áreas de mina AM 2 a AM 10 o Sector Nueva Victoria: Incluye las áreas de mina AM 11 a AM 15 Al interior de las áreas de mina se localizarán los siguientes componentes del proyecto: a) zonas de explotación de caliche; b) centro de operación de manejo de soluciones y; c) centro de operación de mina (servicios generales). El proyecto contempla la operación de un máximo 3 centros de operación de manejo de soluciones y 3 centros de operación de mina, en forma simultánea b. Area Industrial Nueva Victoria (AI-1): corresponde a terrenos ubicados en la zona de uso industrial de "Operación Nueva Victoria". El proyecto en evaluación incluye la ampliación de las actuales instalaciones, mediante la adición de nuevos módulo de producción de yoduro, la ampliación de la actual Planta de Yodo y la implementación de nuevas instalaciones de apoyo. Estas obras involucran una superficie aproximada de 0,08 km2. c. Area Industrial Sur Viejo (AI-2): corresponde a terrenos ubicados en el sector del salar de "Sur Viejo". En este sector se contempla la ampliación del sistema de pozas de evaporación solar, la construcción de una planta de neutralización y una planta productiva de nitratos y la implementación de áreas adicionales de acopio de sales. Estas obras se emplazan sobre una superficie total de 18,8 km2. d. Pozos de agua industrial: Corresponde a la habilitación y aprobación ambiental del total de los derechos de aguas otorgados consuntivos de 11 pozos, - 6 pozos localizados al oeste del Salar de Bellavista (pozos S-16, S-17, BRAC, S-6B, S-3 y S-30) con una tasa total de extracción de 187 l/s, 1 pozo ubicado al este de Salar de Bellavista (pozo TC-9) con una tasa de extracción de 14 l/s, pozo ubicado en el Salar de Pintado (pozo CORFO 688) con una tasa de extracción de 70 l/s y un grupo de 3 pozos localizados en el Salar de Llamara (pozos 3X-14A, 2PL2 y 3X-S7) con una tasa total de 70,7 l/s. Asimismo, se solicita la aprobación ambiental para ejercer la totalidad de los derechos de agua constituidos en 4 pozos localizados en el Salar de Llamara (pozos 2PL3, X-17A, 2HENOC y 3X-16A), es decir, se solicita la aprobación ambiental por un monto de 54 l/s adicional a lo actualmente aprobado. e. Tramos lineales (TL-1 a TL-17, TL-19, TL-20 y TL-22 a TL-24): Corresponden a trazados que indican los tramos donde se instalarán las aducciones de agua industrial, tendidos eléctricos, aducciones de agua feble ácida (AFA), aducciones de brine y/o caminos de servicio, que formarán parte del presente proyecto. El largo total estimado para el conjunto de tramos lineales es de 159 km de franjas de 20 m de ancho, en las que se instalarán una o más de las obras lineales señaladas. 1.4 Cronograma de implementación del proyecto La puesta en marcha se llevará a cabo una vez terminada la construcción, en el mes 13, para comenzar con la etapa de operación en el mes 14, previéndose una vida útil de 30 años. Es preciso señalar que durante la etapa de operación, en forma simultánea a las actividades propias de producción y de acuerdo al avance de las faenas de explotación, el proyecto contempla la construcción de una o más obras en las áreas de mina destinadas a la explotación de caliche. Las posibles obras a construir serán: a) centros de manejo de soluciones, b) centros de operación de mina (servicios generales) y; c) caminos de servicio entre y al interior de las áreas de mina. 1.5 Requerimientos en mano de obra En la etapa de construcción se requerirá un promedio de 636 trabajadores al mes. Se estima un total de 974 trabajadores durante el mes de máximo empleo. La construcción del proyecto tendrá una duración aproximada de 12 meses. Durante la operación del proyecto se estima un promedio de 280 trabajadores por turno, es decir un total de 467 trabajadores en las distintas instalaciones del proyecto (áreas de mina, área industrial de Nueva Victoria y área industrial de Sur Viejo). 1.6 Descripción de las actividades del proyecto A continuación se describen en forma resumida las principales actividades del proyecto, ordenadas según la etapa en la cual estas se ejecutan (construcción, operación y abandono). 1.6.1 Etapa de construcción Las principales actividades a ejecutar durante la construcción del proyecto son: a. Instalación de faenas. Corresponde a la instalación y operación transitoria de infraestructura de apoyo a la labor constructiva. El proyecto contempla la instalación de faenas en las áreas industriales de Nueva Victoria y Sur Viejo, y en las áreas de mina cada vez que se requiera construir un centro de operación en éstas. Por otra parte se contempla la instalación de uno o más campamentos, estos corresponderán a containers habilitados como dormitorios y destinados a una fracción del personal de contratista que pernoctará en el sector de las obras. b. Transporte de insumos, equipos, maquinaria y personal. El transporte de insumos y materiales necesarios para la construcción de las obras se realizará mediante camiones adecuados para el tipo de material y que cumplan con la normativa ambiental vigente. Los equipos se transportarán en camiones, de acuerdo a su peso y dimensiones. Los equipos de grandes dimensiones serán transportados desarmados, en la medida que su diseño y características técnicas lo permitan, de lo contrario se implementarán las medidas necesarias para su transporte. El personal viajara en buses desde y hacia las obras. c. Almacenamiento de materiales e insumos. Los materiales e insumos de construcción serán almacenados en recintos especialmente habilitados para ello. Se requerirá almacenar cantidades significativas de materiales en obra, como moldajes, tuberías, acero, etc. Los lugares destinados al almacenamiento de materiales cumplirán con todas las normas oficiales vigentes. d. Funcionamiento de generadores. Comprende el funcionamiento de generadores, que proporcionarán la energía necesaria para el adecuado funcionamiento de la maquinaria requerida para llevar adelante las faenas constructivas y para iluminación. e. Suministro y transporte de material de relleno. Corresponde a la obtención y transporte de material de relleno necesario para ajustar la topografía a las especificaciones técnicas de las obras proyectadas. El material de relleno a utilizar será suministrado en camiones desde: a) pilas de lixiviación en desuso y; b) la torta de ripios localizada al sur oeste de Victoria. f. Movimientos de tierra y compactación. Comprende el despeje y la limpieza del terreno, la ejecución de excavaciones y rellenos, con el fin de adecuar la topografía del terreno a las especificaciones técnicas y constructivas de las obras proyectadas. Estos movimientos de tierra involucran el uso de maquinaria pesada, como: bulldozers, retroexcavadoras, cargadores frontales, motoniveladoras y camiones tolva. g. Ampliación, mejoramiento y construcción de vías de acceso y caminos. Se refiere a la construcción, ampliación y/o mejoramiento de la red de caminos de servicio, necesaria para la operación del proyecto. Se contempla la construcción o mejoramiento de: a) caminos de servicio entre y al interior de las áreas de mina y áreas industriales; b) caminos de servicios en los tramos lineales y c) camino de acceso al área industrial de Sur Viejo. h. Instalación de aducciones de agua industrial y tuberías para el transporte de brine y AFA. Consiste en: (a) la instalación de tuberías de agua industrial desde los pozos de agua hasta el área industrial de Nueva Victoria y a las áreas de mina; (b) el tendido de tuberías para brine entre los centros de manejo de soluciones ubicados en las áreas de mina y la planta ubicada en el área industrial de Nueva Victoria; y (c) el tendido de tuberías para el transporte de AFA entre la planta de Nueva Victoria y las pilas de lixiviación localizadas en las áreas de mina. i. Instalación, reubicación y/o ampliación del tendido eléctrico. Consiste en la instalación, reubicación y/o ampliación del tendido eléctrico y transformadores necesarios para los requerimientos energéticos del proyecto. El proyecto contempla la instalación de transformadores en cada centro de operación, de una potencia estimada entre 2,21 a 2,05 MVA. Por otra parte, en el caso de los pozos de agua industrial ha habilitar se contempla la instalación de transformadores de 23/0,4 kV y la instalación de un tendido eléctrico paralelo al trazado de las aducciones de agua industrial. j. Habilitación de pozos de agua industrial. Consiste en la ejecución de las obras necesarias para la operación de los pozos de agua industrial a las tasas de extracción de agua requeridas por el proyecto. k. Construcción de fundaciones, radieres, estructuras, canchas de acopio, pozas e instalaciones de apoyo. Se refiere a la construcción de fundaciones y radieres y a la instalación de las estructuras y edificaciones necesarias para el soporte de equipos y maquinaria e infraestructura de apoyo. Incluye actividades de construcción de canchas de acopio, pozas, la instalación del sistema de impermeabilización y del sistema de detección y control de fugas, entre otras. l. Montaje de equipos. Comprende la instalación de los equipos necesarios para el proceso productivo. Su montaje se realizará utilizando grúas y otros elementos de izamiento. m. Mantención de equipos y maquinaria de construcción. Comprende las actividades propias de la mantención de los equipos y maquinaria, para su adecuado funcionamiento. Todas estas actividades se realizarán en lugares habilitados y con personal capacitado y según las indicaciones y frecuencias especificadas por los fabricantes. n. Manejo de aguas servidas: Las instalaciones de faena contarán con instalaciones de servicios generales con su correspondiente planta de tratamiento de aguas servidas y/o baños químicos. o. Manejo de residuos sólidos. Los residuos sólidos generados serán recolectados, transportados y depositados por una empresa autorizada, en los vertederos existentes y autorizados, de acuerdo a sus características (residuos domésticos, industrial, escombros, etc.). p. Cierre de faenas constructivas. Esta actividad se realizará al término del período de construcción, y contempla el desarme de las instalaciones de faenas en caso necesario y la disposición final de todos los residuos de construcción, en los vertederos mencionados anteriormente. 1.6.2 Etapa de operación El proceso de producción a emplear en el presente proyecto, es muy similar al que actualmente se encuentra en operación en las instalaciones industriales de Nueva Victoria y de Sur Viejo. La principal diferencia radica en el posterior tratamiento al que serán sometidas las sales ricas en nitrato obtenidas desde las pozas de evaporación solar. Actualmente estas son acumuladas en canchas de acopio. El presente proyecto permitirá su procesamiento, mediante la instalación y operación de una Planta de Nitratos. La Figura 1.2 presenta en forma esquemática los principales componentes del proceso productivo. A continuación se describen los principales procesos que se llevarán a cabo durante la operación del proyecto: a. Faenas en áreas de mina. El proyecto contempla la extracción de caliche (materia prima) desde las áreas de mina. En primer lugar, se removerá la sobrecarga, la que se depositará en sectores próximos ya explotados o carentes de mineral. Luego, el caliche se extraerá mediante el uso de explosivos, para posteriormente, ser cargado en camiones de alto tonelaje los que efectuarán el traslado del mineral al sector donde se realizará el proceso de lixiviación en pilas. La lixiviación en pilas, consistirá en el riego del caliche con una mezcla de agua industrial y AFA (agua feble ácida), proceso que generará una solución rica en minerales (brine). b. Producción de yoduro La solución obtenida de las pilas "brine" será enviada a través de un sistema de bombas y cañerías a las instalaciones de producción de yoduro, donde en forma conjunta con varios insumos (agua, kerosén, ácido sulfúrico o hidróxido de sodio líquido, azufre, cloro y auxiliar filtrante) se obtendrá una solución concentrada de yoduro, y una corriente residual de agua feble ácida (AFA). Cabe señalar, que como alternativa a este proceso se contempla el utilizar "solución de yoduro" proveniente de otras instalaciones de producción de SQM. c. Producción de yodo. La solución concentrada de yoduro, será enviada a la planta de producción de yodo, en la cual a través de una serie de procesos y de la incorporación de diversos insumos (agua, auxiliar filtrante, hidróxido de sodio, peróxido de hidrógeno, carbón activado, ácido sulfonítrico, agua tratada y meta bisulfito de sodio, etc.) se obtendrá como producto final "yodo prilado". Este será envasado y almacenado, quedando listo para ser enviado a su destino final. d. Neutralización de AFA. El agua feble ácida (AFA) generada durante la producción de yoduro se reutilizará en dos procesos: (a) una parte será recirculada hacia las áreas de mina, en particular al proceso de lixiviación en pilas y (b) la fracción restante será enviada a las plantas de neutralización, en Sur Viejo, donde por medio de la adición de una solución de cal se producirá AFN ("agua feble neutra"). Esta última, será enviada al sistema de pozas de evaporación solar. e. Operación de sistema de pozas. El sistema de pozas de evaporación solar es una unidad funcional que implica: a) las pozas, b) los trasvases, c) los sistemas de cosecha y d) transporte de sales. Las pozas recibirán el AFN proveniente de las plantas de neutralización, su objetivo fundamental es evaporar el agua, separar las sales de descarte y cosechar las sales con alta ley en nitrato de sodio (NaNO3). Las sales de descarte se depositarán en canchas de acopio, que contarán con sistema de impermeabilización (carpeta de polietileno de alta densidad "HDPE" de 1 mm de espesor) y drenaje, lo que permitirá recuperar las soluciones drenadas y retornarlas a las pozas mediante bombeo. Las sales de producción ricas en nitrato serán almacenadas en canchas impermeabilizadas (con una carpeta de HDPE de 1 mm de espesor), para ser posteriormente transportadas hasta la nueva Planta de Nitratos o a otras plantas de procesamiento perteneciente a SQM. f. Producción de nitrato de sodio y/o nitrato de potasio. Las sales ricas en nitrato provenientes del sistema de pozas de evaporación que sean enviadas a la nueva Planta de Nitratos serán procesadas para producir nitrato de sodio o nitrato de potasio. Las materias primas necesarias para la producción de estos productos, son: (a) sales ricas en nitrato provenientes de las pozas de evaporación; (b) agua industrial; y (c) cloruro de potasio (utilizado en la producción de nitrato de potasio). El producto será almacenado y dispuesto en una cancha de acopio impermeabilizada, para luego ser cargado y transportado a su destino final. 1.6.3 Etapa de abandono Durante la etapa de abandono del proyecto, se contempla la ejecución de las actividades que se detallan a continuación. a. Estabilización de los taludes. En caso de ser necesario, se procederá a la estabilización de los taludes de los acopios de sobrecarga y/o pilas de caliche remanente. b. Desmantelamiento de instalaciones. Se retirarán aquellas instalaciones o estructuras necesarias para evitar condiciones de riesgo. Dependiendo de las condiciones del mercado, se intentará su venta o utilización en otras instalaciones. En caso que esto no sea posible, se enviarán a un depósito cercano que, a dicha fecha, esté autorizado para su recepción. c. Cierre de almacenes de explosivos. Se cerrarán los almacenes para explosivos. d. Instalación de letreros de advertencia. En el sector de pozas y en cualquier otra estructura remanente se instalarán letreros de advertencia. e. Desenergización de las instalaciones. Se desenergización las instalaciones eléctricas. f. Cierre de accesos. Se cerrarán todos los accesos a instalaciones y caminos de servicios. Se instalarán las señalizaciones correspondientes. g. Disposición de residuos. Los residuos se dispondrán de acuerdo a sus características en vertederos autorizados. Los únicos residuos de operación que permanecerá en el lugar serán los acopios de sales de descarte, borras y yeso, dado lo inocuo de éstos, no se requerirán letreros de advertencia ni cierre perimetral. Las actividades señaladas se efectuarían en total concordancia con las disposiciones legales vigentes a la fecha de cierre del proyecto, en especial aquéllas referidas a la protección de los trabajadores y del medio ambiente. 1.7 Caracterización de emisiones, descargas y residuos 1.8 Emisiones a la atmósfera Tal como se señala en el Capítulo 6 del EIA, las emisiones atmosféricas se refieren principalmente a material particulado y dióxido de azufre, y su magnitud no representan riesgo para la salud de la población. Con respecto a la emisión de gases de combustión derivada de vehículos y maquinaria motorizada ésta es mínima. Adicionalmente, el proyecto contempla la implementación de una serie de medidas control cuyo objetivo es minimizar de las emisiones atmosféricas y asegurar el cumplimiento de la normativa vigente. Producto de los resultados obtenidos, de las medidas de mitigación señaladas en el EIA y de la lejanía de las obras con el centro poblado más cercano4, el impacto de las emisiones atmosféricas emitidas durante las etapas de construcción y operación sobre la calidad del aire no es significativo. La Tabla 1.3 presenta las fuentes identificadas, el tipo de emisión, la duración de ésta y su frecuencia. 1.9 Efluentes líquidos Durante la etapa de construcción no se generarán residuos industriales y/o mineros líquidos. Las aguas servidas generadas durante esta etapa serán manejadas en plantas de tratamiento de aguas servidas y/o baños químicos cuyos residuos serán retirados por empresas autorizadas del rubro. Durante la etapa de operación se generarán el siguiente residuo industriales líquidos, adicional a la situación actual: efluente de las plantas de agua potable (el efluente generado en la planta de osmosis inversa se dispondrá como agua industrial o para riego de caminos). Las aguas servidas serán tratadas en plantas de tratamiento nuevas y existentes, cuyos residuos serán retirados por empresas autorizadas del rubro. La Tabla 1.4 presenta las fuentes identificadas, la etapa del proyecto, el caudal promedio y la duración de la descarga. 1.10 Residuos sólidos En la etapa de construcción se generarán los siguientes residuos sólidos: (a) residuos inertes (material extraído en las excavaciones y escombros) serán utilizados en el mismo sector para conformar plataformas y/o transportados en camión y depositados en el vertedero existente y autorizado para este tipo de residuos en Nueva Victoria; (b) basuras domésticas serán recolectadas y transportadas en camión, disponiéndose en el vertedero existente y autorizado para basuras domésticas localizado en Nueva Victoria y; (c) otros residuos sólidos (envases vacíos, clavos, fierros, restos de tuberías, etc.) serán dispuestos en un vertedero existente y autorizado para residuos industriales en Nueva Victoria. En esta etapa, no se generarán residuos industriales y/o mineros sólidos. Durante la operación, se generarán los siguientes residuos sólidos: (a) sobrecarga, será apilada en sectores ya explotados o carentes de mineral (residuo absolutamente neutro que no presenta riesgos ambientales), (b) yeso, generado en la Planta de Neutralización, será dispuesto en una cancha de acopio en el sector de Sur Viejo; (c) sales de descarte, producidas en las pozas de evaporación y Planta de Nitratos, serán dispuestas en una cancha de acopio de sales en el área industrial de Sur Viejo, (d) las borras y residuos de la limpieza de filtros producidos en la Planta de Yoduro, serán depositados en una poza de almacenamiento de borras en el área industrial de Nueva Victoria (e) basuras domésticas, serán manejadas de igual forma que en la etapa de construcción, (f) residuos industriales, serán dispuestos en el vertedero para residuos industriales existente y autorizado en Nueva Victoria y (g) residuos peligrosos, se dispondrán en el vertedero para residuos peligrosos existente y autorizado en Nueva Victoria. 1.11 Ruido El aumento de ruido, medido en términos del nivel de presión sonora equivalente (NPSeq), durante la etapa de construcción está básicamente ligado a la operación de equipos de movimiento de tierras e izamiento, tránsito de camiones, funcionamiento de la maquinaria de construcción y a los generadores. Se estima que el nivel máximo de ruido, que ocurriría en períodos muy acotados de tiempo, debido a la construcción del proyecto, sería menor a 120 dB(A). En la etapa de operación, las principales fuentes de ruido corresponderán a la explotación de mina y tránsito de camiones, con un valor aproximado de 120 dB(A). Cabe señalar, que los sectores de explotación de caliche y áreas industriales, corresponden a zonas actualmente despobladas, donde el centro poblado más cercano - Victoria, localidad situada al borde de la Ruta 5, próxima a la antigua Ex Oficina Victoria -, se encuentra a 4 km de distancia del área de mina más cercana (AM-6) y a 25 km al norte de las instalaciones industriales del complejo Operación Nueva Victoria. Por su parte, aunque existe una menor distancia entre los tramos lineales -correspondiente a la aducción de agua industrial, brine y AFA y la localidad de Victoria (0,8 km), la emisión de las fuentes de ruido asociadas a estos componentes lineales es no significativa. Se considera que durante la operación, las emisiones acústicas no serán percibidas en el límite de las instalaciones de SQM. El bajo nivel de inmisión de ruido estimado para las distintas etapas del proyecto indica que se dará cumplimiento a los límites establecidos en el D.S. N°146/1997 del Ministerio Secretaría General de la Presidencia. Por otra parte, el cumplimiento de la normativa incluida en el D.S. Nº 594/1999 del Ministerio de Salud ("Reglamento sobre Condiciones Sanitarias y Ambientales Básicas en los Lugares de Trabajo"), estará garantizado a través de la implementación del Programa de Salud Ocupacional orientado a proteger la salud de los trabajadores.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Proyecto Gasoducto del Pacífico Lateral Charrúa</t>
+          <t>Soronal</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>1407942</t>
+          <t>1314604</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1407942&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1314604&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Interregional</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>231,000</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>24/04/2006</t>
+          <t>08/02/2006</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Aprobado</t>
+          <t>Desistido</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Declaración de Impacto Ambiental</t>
+          <t>Estudio de Impacto Ambiental</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Gasoductos</t>
+          <t>Proyecto de desarrollo minero sobre 5000 tons/mens</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Gasoducto del Pacífico S.A.</t>
+          <t>SQM Industrial S.A.</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>Geobiota</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>1.1 Antecedentes generales El proyecto "Soronal" se emplaza en la comuna de Pozo Almonte, I Región de Tarapacá, su titular es SQM S.A. y contempla una inversión de US$ 231.000.000, la que se haría gradualmente durante la vida útil de 30 años del proyecto. El principal objetivo del proyecto es aumentar la capacidad de actual de yodo en 6.000 ton/año, alcanzando una capacidad de 10.500 ton/año1, en las instalaciones del complejo industrial Operación Nueva Victoria y una capacidad de producción de 900.000 ton/año de nitrato de sodio y/o nitrato de potasio en las instalaciones industriales de Sur Viejo. A fin de satisfacer este objetivo, el proyecto contempla: o Incorporar 248,8 km2 de nuevas áreas de mina, con una tasa de extracción máxima de caliche de 35.000.000 ton/año 2; o Aumentar la capacidad de producción de yoduro en un monto equivalente a 7.000 ton/año de yodo; 3 o Aumentar la capacidad productiva de la planta de yodo en 6.000 ton/año; o Aumentar área de evaporación solar para producción de sales de nitrato; o Incorporar una nueva planta de proceso para la producción de nitrato de sodio y/o nitrato de potasio (Planta de Nitratos); o Habilitar y ejercer el total de los derechos de agua de 11 pozos, localizados al oeste del Salar de Bellavista (6 pozos), al este del Salar de Bellavista (1pozo), en el Salar de Pintado (1 pozo) y en el Salar de Llamara (3 pozos), y ejercer el total de los derechos de agua constituidos en 4 pozos actualmente habilitados en el Salar de Llamara. La ejecución de este proyecto obedece a un incremento observable en la demanda de yodo y de nitrato a nivel mundial. Lo que genera la necesidad de contar con instalaciones que permitan satisfacer dicha demanda en los próximos años. El proyecto contempla planes de seguimiento ambiental, planes de contingencias y una serie de medidas especialmente diseñadas para fortalecer una operación ambientalmente segura. 1.2 Localización geográfica y administrativa El proyecto se localiza en la Primera Región de Tarapacá, provincia de Iquique, comuna de Pozo Almonte. Específicamente, a unos 145 km al sureste de la ciudad de Iquique y a unos 25 km al sur de Pozo Almonte, en un área circunscrita por las coordenadas N: 7.657.992 y N: 7.736.401 y las coordenadas E: 409.150 y E: 450.345. 1.3 Componentes del proyecto y superficie involucrada A continuación se presenta una breve descripción de las diferentes obras que forman parte del proyecto. a. Areas de mina (AM): Corresponden a quince nuevas áreas de explotación de caliche, las que involucran una superficie total de 248,8 km2. Estas áreas se agrupan en tres grandes sectores, a saber: o Sector Coruña: Incluye el área de mina AM 1 o Sector Soronal: Incluye las áreas de mina AM 2 a AM 10 o Sector Nueva Victoria: Incluye las áreas de mina AM 11 a AM 15 Al interior de las áreas de mina se localizarán los siguientes componentes del proyecto: a) zonas de explotación de caliche; b) centro de operación de manejo de soluciones y; c) centro de operación de mina (servicios generales). El proyecto contempla la operación de un máximo 3 centros de operación de manejo de soluciones y 3 centros de operación de mina, en forma simultánea b. Area Industrial Nueva Victoria (AI-1): corresponde a terrenos ubicados en la zona de uso industrial de "Operación Nueva Victoria". El proyecto en evaluación incluye la ampliación de las actuales instalaciones, mediante la adición de nuevos módulo de producción de yoduro, la ampliación de la actual Planta de Yodo y la implementación de nuevas instalaciones de apoyo. Estas obras involucran una superficie aproximada de 0,08 km2. c. Area Industrial Sur Viejo (AI-2): corresponde a terrenos ubicados en el sector del salar de "Sur Viejo". En este sector se contempla la ampliación del sistema de pozas de evaporación solar, la construcción de una planta de neutralización y una planta productiva de nitratos y la implementación de áreas adicionales de acopio de sales. Estas obras se emplazan sobre una superficie total de 18,8 km2. d. Pozos de agua industrial: Corresponde a la habilitación y aprobación ambiental del total de los derechos de aguas otorgados consuntivos de 11 pozos, - 6 pozos localizados al oeste del Salar de Bellavista (pozos S-16, S-17, BRAC, S-6B, S-3 y S-30) con una tasa total de extracción de 187 l/s, 1 pozo ubicado al este de Salar de Bellavista (pozo TC-9) con una tasa de extracción de 14 l/s, pozo ubicado en el Salar de Pintado (pozo CORFO 688) con una tasa de extracción de 70 l/s y un grupo de 3 pozos localizados en el Salar de Llamara (pozos 3X-14A, 2PL2 y 3X-S7) con una tasa total de 70,7 l/s. Asimismo, se solicita la aprobación ambiental para ejercer la totalidad de los derechos de agua constituidos en 4 pozos localizados en el Salar de Llamara (pozos 2PL3, X-17A, 2HENOC y 3X-16A), es decir, se solicita la aprobación ambiental por un monto de 54 l/s adicional a lo actualmente aprobado. e. Tramos lineales (TL-1 a TL-17, TL-19, TL-20 y TL-22 a TL-24): Corresponden a trazados que indican los tramos donde se instalarán las aducciones de agua industrial, tendidos eléctricos, aducciones de agua feble ácida (AFA), aducciones de brine y/o caminos de servicio, que formarán parte del presente proyecto. El largo total estimado para el conjunto de tramos lineales es de 159 km de franjas de 20 m de ancho, en las que se instalarán una o más de las obras lineales señaladas. 1.4 Cronograma de implementación del proyecto La puesta en marcha se llevará a cabo una vez terminada la construcción, en el mes 13, para comenzar con la etapa de operación en el mes 14, previéndose una vida útil de 30 años. Es preciso señalar que durante la etapa de operación, en forma simultánea a las actividades propias de producción y de acuerdo al avance de las faenas de explotación, el proyecto contempla la construcción de una o más obras en las áreas de mina destinadas a la explotación de caliche. Las posibles obras a construir serán: a) centros de manejo de soluciones, b) centros de operación de mina (servicios generales) y; c) caminos de servicio entre y al interior de las áreas de mina. 1.5 Requerimientos en mano de obra En la etapa de construcción se requerirá un promedio de 636 trabajadores al mes. Se estima un total de 974 trabajadores durante el mes de máximo empleo. La construcción del proyecto tendrá una duración aproximada de 12 meses. Durante la operación del proyecto se estima un promedio de 280 trabajadores por turno, es decir un total de 467 trabajadores en las distintas instalaciones del proyecto (áreas de mina, área industrial de Nueva Victoria y área industrial de Sur Viejo). 1.6 Descripción de las actividades del proyecto A continuación se describen en forma resumida las principales actividades del proyecto, ordenadas según la etapa en la cual estas se ejecutan (construcción, operación y abandono). 1.6.1 Etapa de construcción Las principales actividades a ejecutar durante la construcción del proyecto son: a. Instalación de faenas. Corresponde a la instalación y operación transitoria de infraestructura de apoyo a la labor constructiva. El proyecto contempla la instalación de faenas en las áreas industriales de Nueva Victoria y Sur Viejo, y en las áreas de mina cada vez que se requiera construir un centro de operación en éstas. Por otra parte se contempla la instalación de uno o más campamentos, estos corresponderán a containers habilitados como dormitorios y destinados a una fracción del personal de contratista que pernoctará en el sector de las obras. b. Transporte de insumos, equipos, maquinaria y personal. El transporte de insumos y materiales necesarios para la construcción de las obras se realizará mediante camiones adecuados para el tipo de material y que cumplan con la normativa ambiental vigente. Los equipos se transportarán en camiones, de acuerdo a su peso y dimensiones. Los equipos de grandes dimensiones serán transportados desarmados, en la medida que su diseño y características técnicas lo permitan, de lo contrario se implementarán las medidas necesarias para su transporte. El personal viajara en buses desde y hacia las obras. c. Almacenamiento de materiales e insumos. Los materiales e insumos de construcción serán almacenados en recintos especialmente habilitados para ello. Se requerirá almacenar cantidades significativas de materiales en obra, como moldajes, tuberías, acero, etc. Los lugares destinados al almacenamiento de materiales cumplirán con todas las normas oficiales vigentes. d. Funcionamiento de generadores. Comprende el funcionamiento de generadores, que proporcionarán la energía necesaria para el adecuado funcionamiento de la maquinaria requerida para llevar adelante las faenas constructivas y para iluminación. e. Suministro y transporte de material de relleno. Corresponde a la obtención y transporte de material de relleno necesario para ajustar la topografía a las especificaciones técnicas de las obras proyectadas. El material de relleno a utilizar será suministrado en camiones desde: a) pilas de lixiviación en desuso y; b) la torta de ripios localizada al sur oeste de Victoria. f. Movimientos de tierra y compactación. Comprende el despeje y la limpieza del terreno, la ejecución de excavaciones y rellenos, con el fin de adecuar la topografía del terreno a las especificaciones técnicas y constructivas de las obras proyectadas. Estos movimientos de tierra involucran el uso de maquinaria pesada, como: bulldozers, retroexcavadoras, cargadores frontales, motoniveladoras y camiones tolva. g. Ampliación, mejoramiento y construcción de vías de acceso y caminos. Se refiere a la construcción, ampliación y/o mejoramiento de la red de caminos de servicio, necesaria para la operación del proyecto. Se contempla la construcción o mejoramiento de: a) caminos de servicio entre y al interior de las áreas de mina y áreas industriales; b) caminos de servicios en los tramos lineales y c) camino de acceso al área industrial de Sur Viejo. h. Instalación de aducciones de agua industrial y tuberías para el transporte de brine y AFA. Consiste en: (a) la instalación de tuberías de agua industrial desde los pozos de agua hasta el área industrial de Nueva Victoria y a las áreas de mina; (b) el tendido de tuberías para brine entre los centros de manejo de soluciones ubicados en las áreas de mina y la planta ubicada en el área industrial de Nueva Victoria; y (c) el tendido de tuberías para el transporte de AFA entre la planta de Nueva Victoria y las pilas de lixiviación localizadas en las áreas de mina. i. Instalación, reubicación y/o ampliación del tendido eléctrico. Consiste en la instalación, reubicación y/o ampliación del tendido eléctrico y transformadores necesarios para los requerimientos energéticos del proyecto. El proyecto contempla la instalación de transformadores en cada centro de operación, de una potencia estimada entre 2,21 a 2,05 MVA. Por otra parte, en el caso de los pozos de agua industrial ha habilitar se contempla la instalación de transformadores de 23/0,4 kV y la instalación de un tendido eléctrico paralelo al trazado de las aducciones de agua industrial. j. Habilitación de pozos de agua industrial. Consiste en la ejecución de las obras necesarias para la operación de los pozos de agua industrial a las tasas de extracción de agua requeridas por el proyecto. k. Construcción de fundaciones, radieres, estructuras, canchas de acopio, pozas e instalaciones de apoyo. Se refiere a la construcción de fundaciones y radieres y a la instalación de las estructuras y edificaciones necesarias para el soporte de equipos y maquinaria e infraestructura de apoyo. Incluye actividades de construcción de canchas de acopio, pozas, la instalación del sistema de impermeabilización y del sistema de detección y control de fugas, entre otras. l. Montaje de equipos. Comprende la instalación de los equipos necesarios para el proceso productivo. Su montaje se realizará utilizando grúas y otros elementos de izamiento. m. Mantención de equipos y maquinaria de construcción. Comprende las actividades propias de la mantención de los equipos y maquinaria, para su adecuado funcionamiento. Todas estas actividades se realizarán en lugares habilitados y con personal capacitado y según las indicaciones y frecuencias especificadas por los fabricantes. n. Manejo de aguas servidas: Las instalaciones de faena contarán con instalaciones de servicios generales con su correspondiente planta de tratamiento de aguas servidas y/o baños químicos. o. Manejo de residuos sólidos. Los residuos sólidos generados serán recolectados, transportados y depositados por una empresa autorizada, en los vertederos existentes y autorizados, de acuerdo a sus características (residuos domésticos, industrial, escombros, etc.). p. Cierre de faenas constructivas. Esta actividad se realizará al término del período de construcción, y contempla el desarme de las instalaciones de faenas en caso necesario y la disposición final de todos los residuos de construcción, en los vertederos mencionados anteriormente. 1.6.2 Etapa de operación El proceso de producción a emplear en el presente proyecto, es muy similar al que actualmente se encuentra en operación en las instalaciones industriales de Nueva Victoria y de Sur Viejo. La principal diferencia radica en el posterior tratamiento al que serán sometidas las sales ricas en nitrato obtenidas desde las pozas de evaporación solar. Actualmente estas son acumuladas en canchas de acopio. El presente proyecto permitirá su procesamiento, mediante la instalación y operación de una Planta de Nitratos. La Figura 1.2 presenta en forma esquemática los principales componentes del proceso productivo. A continuación se describen los principales procesos que se llevarán a cabo durante la operación del proyecto: a. Faenas en áreas de mina. El proyecto contempla la extracción de caliche (materia prima) desde las áreas de mina. En primer lugar, se removerá la sobrecarga, la que se depositará en sectores próximos ya explotados o carentes de mineral. Luego, el caliche se extraerá mediante el uso de explosivos, para posteriormente, ser cargado en camiones de alto tonelaje los que efectuarán el traslado del mineral al sector donde se realizará el proceso de lixiviación en pilas. La lixiviación en pilas, consistirá en el riego del caliche con una mezcla de agua industrial y AFA (agua feble ácida), proceso que generará una solución rica en minerales (brine). b. Producción de yoduro La solución obtenida de las pilas "brine" será enviada a través de un sistema de bombas y cañerías a las instalaciones de producción de yoduro, donde en forma conjunta con varios insumos (agua, kerosén, ácido sulfúrico o hidróxido de sodio líquido, azufre, cloro y auxiliar filtrante) se obtendrá una solución concentrada de yoduro, y una corriente residual de agua feble ácida (AFA). Cabe señalar, que como alternativa a este proceso se contempla el utilizar "solución de yoduro" proveniente de otras instalaciones de producción de SQM. c. Producción de yodo. La solución concentrada de yoduro, será enviada a la planta de producción de yodo, en la cual a través de una serie de procesos y de la incorporación de diversos insumos (agua, auxiliar filtrante, hidróxido de sodio, peróxido de hidrógeno, carbón activado, ácido sulfonítrico, agua tratada y meta bisulfito de sodio, etc.) se obtendrá como producto final "yodo prilado". Este será envasado y almacenado, quedando listo para ser enviado a su destino final. d. Neutralización de AFA. El agua feble ácida (AFA) generada durante la producción de yoduro se reutilizará en dos procesos: (a) una parte será recirculada hacia las áreas de mina, en particular al proceso de lixiviación en pilas y (b) la fracción restante será enviada a las plantas de neutralización, en Sur Viejo, donde por medio de la adición de una solución de cal se producirá AFN ("agua feble neutra"). Esta última, será enviada al sistema de pozas de evaporación solar. e. Operación de sistema de pozas. El sistema de pozas de evaporación solar es una unidad funcional que implica: a) las pozas, b) los trasvases, c) los sistemas de cosecha y d) transporte de sales. Las pozas recibirán el AFN proveniente de las plantas de neutralización, su objetivo fundamental es evaporar el agua, separar las sales de descarte y cosechar las sales con alta ley en nitrato de sodio (NaNO3). Las sales de descarte se depositarán en canchas de acopio, que contarán con sistema de impermeabilización (carpeta de polietileno de alta densidad "HDPE" de 1 mm de espesor) y drenaje, lo que permitirá recuperar las soluciones drenadas y retornarlas a las pozas mediante bombeo. Las sales de producción ricas en nitrato serán almacenadas en canchas impermeabilizadas (con una carpeta de HDPE de 1 mm de espesor), para ser posteriormente transportadas hasta la nueva Planta de Nitratos o a otras plantas de procesamiento perteneciente a SQM. f. Producción de nitrato de sodio y/o nitrato de potasio. Las sales ricas en nitrato provenientes del sistema de pozas de evaporación que sean enviadas a la nueva Planta de Nitratos serán procesadas para producir nitrato de sodio o nitrato de potasio. Las materias primas necesarias para la producción de estos productos, son: (a) sales ricas en nitrato provenientes de las pozas de evaporación; (b) agua industrial; y (c) cloruro de potasio (utilizado en la producción de nitrato de potasio). El producto será almacenado y dispuesto en una cancha de acopio impermeabilizada, para luego ser cargado y transportado a su destino final. 1.6.3 Etapa de abandono Durante la etapa de abandono del proyecto, se contempla la ejecución de las actividades que se detallan a continuación. a. Estabilización de los taludes. En caso de ser necesario, se procederá a la estabilización de los taludes de los acopios de sobrecarga y/o pilas de caliche remanente. b. Desmantelamiento de instalaciones. Se retirarán aquellas instalaciones o estructuras necesarias para evitar condiciones de riesgo. Dependiendo de las condiciones del mercado, se intentará su venta o utilización en otras instalaciones. En caso que esto no sea posible, se enviarán a un depósito cercano que, a dicha fecha, esté autorizado para su recepción. c. Cierre de almacenes de explosivos. Se cerrarán los almacenes para explosivos. d. Instalación de letreros de advertencia. En el sector de pozas y en cualquier otra estructura remanente se instalarán letreros de advertencia. e. Desenergización de las instalaciones. Se desenergización las instalaciones eléctricas. f. Cierre de accesos. Se cerrarán todos los accesos a instalaciones y caminos de servicios. Se instalarán las señalizaciones correspondientes. g. Disposición de residuos. Los residuos se dispondrán de acuerdo a sus características en vertederos autorizados. Los únicos residuos de operación que permanecerá en el lugar serán los acopios de sales de descarte, borras y yeso, dado lo inocuo de éstos, no se requerirán letreros de advertencia ni cierre perimetral. Las actividades señaladas se efectuarían en total concordancia con las disposiciones legales vigentes a la fecha de cierre del proyecto, en especial aquéllas referidas a la protección de los trabajadores y del medio ambiente. 1.7 Caracterización de emisiones, descargas y residuos 1.8 Emisiones a la atmósfera Tal como se señala en el Capítulo 6 del EIA, las emisiones atmosféricas se refieren principalmente a material particulado y dióxido de azufre, y su magnitud no representan riesgo para la salud de la población. Con respecto a la emisión de gases de combustión derivada de vehículos y maquinaria motorizada ésta es mínima. Adicionalmente, el proyecto contempla la implementación de una serie de medidas control cuyo objetivo es minimizar de las emisiones atmosféricas y asegurar el cumplimiento de la normativa vigente. Producto de los resultados obtenidos, de las medidas de mitigación señaladas en el EIA y de la lejanía de las obras con el centro poblado más cercano4, el impacto de las emisiones atmosféricas emitidas durante las etapas de construcción y operación sobre la calidad del aire no es significativo. La Tabla 1.3 presenta las fuentes identificadas, el tipo de emisión, la duración de ésta y su frecuencia. 1.9 Efluentes líquidos Durante la etapa de construcción no se generarán residuos industriales y/o mineros líquidos. Las aguas servidas generadas durante esta etapa serán manejadas en plantas de tratamiento de aguas servidas y/o baños químicos cuyos residuos serán retirados por empresas autorizadas del rubro. Durante la etapa de operación se generarán el siguiente residuo industriales líquidos, adicional a la situación actual: efluente de las plantas de agua potable (el efluente generado en la planta de osmosis inversa se dispondrá como agua industrial o para riego de caminos). Las aguas servidas serán tratadas en plantas de tratamiento nuevas y existentes, cuyos residuos serán retirados por empresas autorizadas del rubro. La Tabla 1.4 presenta las fuentes identificadas, la etapa del proyecto, el caudal promedio y la duración de la descarga. 1.10 Residuos sólidos En la etapa de construcción se generarán los siguientes residuos sólidos: (a) residuos inertes (material extraído en las excavaciones y escombros) serán utilizados en el mismo sector para conformar plataformas y/o transportados en camión y depositados en el vertedero existente y autorizado para este tipo de residuos en Nueva Victoria; (b) basuras domésticas serán recolectadas y transportadas en camión, disponiéndose en el vertedero existente y autorizado para basuras domésticas localizado en Nueva Victoria y; (c) otros residuos sólidos (envases vacíos, clavos, fierros, restos de tuberías, etc.) serán dispuestos en un vertedero existente y autorizado para residuos industriales en Nueva Victoria. En esta etapa, no se generarán residuos industriales y/o mineros sólidos. Durante la operación, se generarán los siguientes residuos sólidos: (a) sobrecarga, será apilada en sectores ya explotados o carentes de mineral (residuo absolutamente neutro que no presenta riesgos ambientales), (b) yeso, generado en la Planta de Neutralización, será dispuesto en una cancha de acopio en el sector de Sur Viejo; (c) sales de descarte, producidas en las pozas de evaporación y Planta de Nitratos, serán dispuestas en una cancha de acopio de sales en el área industrial de Sur Viejo, (d) las borras y residuos de la limpieza de filtros producidos en la Planta de Yoduro, serán depositados en una poza de almacenamiento de borras en el área industrial de Nueva Victoria (e) basuras domésticas, serán manejadas de igual forma que en la etapa de construcción, (f) residuos industriales, serán dispuestos en el vertedero para residuos industriales existente y autorizado en Nueva Victoria y (g) residuos peligrosos, se dispondrán en el vertedero para residuos peligrosos existente y autorizado en Nueva Victoria. 1.11 Ruido El aumento de ruido, medido en términos del nivel de presión sonora equivalente (NPSeq), durante la etapa de construcción está básicamente ligado a la operación de equipos de movimiento de tierras e izamiento, tránsito de camiones, funcionamiento de la maquinaria de construcción y a los generadores. Se estima que el nivel máximo de ruido, que ocurriría en períodos muy acotados de tiempo, debido a la construcción del proyecto, sería menor a 120 dB(A). En la etapa de operación, las principales fuentes de ruido corresponderán a la explotación de mina y tránsito de camiones, con un valor aproximado de 120 dB(A). Cabe señalar, que los sectores de explotación de caliche y áreas industriales, corresponden a zonas actualmente despobladas, donde el centro poblado más cercano - Victoria, localidad situada al borde de la Ruta 5, próxima a la antigua Ex Oficina Victoria -, se encuentra a 4 km de distancia del área de mina más cercana (AM-6) y a 25 km al norte de las instalaciones industriales del complejo Operación Nueva Victoria. Por su parte, aunque existe una menor distancia entre los tramos lineales -correspondiente a la aducción de agua industrial, brine y AFA y la localidad de Victoria (0,8 km), la emisión de las fuentes de ruido asociadas a estos componentes lineales es no significativa. Se considera que durante la operación, las emisiones acústicas no serán percibidas en el límite de las instalaciones de SQM. El bajo nivel de inmisión de ruido estimado para las distintas etapas del proyecto indica que se dará cumplimiento a los límites establecidos en el D.S. N°146/1997 del Ministerio Secretaría General de la Presidencia. Por otra parte, el cumplimiento de la normativa incluida en el D.S. Nº 594/1999 del Ministerio de Salud ("Reglamento sobre Condiciones Sanitarias y Ambientales Básicas en los Lugares de Trabajo"), estará garantizado a través de la implementación del Programa de Salud Ocupacional orientado a proteger la salud de los trabajadores.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Proyecto Parque Señora Rosario</t>
+          <t>Proyecto Gasoducto del Pacífico Lateral Charrúa</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>1458118</t>
+          <t>1407942</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1458118&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1407942&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Tercera</t>
+          <t>Interregional</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>117,600</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>31/05/2006</t>
+          <t>24/04/2006</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -20895,12 +20900,12 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Centrales generadoras de energía mayores a 3 MW</t>
+          <t>Gasoductos</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Acciona Energía Chile SpA</t>
+          <t>Gasoducto del Pacífico S.A.</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -20912,22 +20917,22 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Proyecto Parque Señora Gabriela</t>
+          <t>Proyecto Parque Señora Rosario</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>1460575</t>
+          <t>1458118</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1460575&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1458118&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -20937,17 +20942,17 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>193,200</t>
+          <t>117,600</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>26/05/2006</t>
+          <t>31/05/2006</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Desistido</t>
+          <t>Aprobado</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -20974,22 +20979,22 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Proyecto Parque San Blas</t>
+          <t>Proyecto Parque Señora Gabriela</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>1460619</t>
+          <t>1460575</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1460619&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1460575&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -20999,7 +21004,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>60,900</t>
+          <t>193,200</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -21036,42 +21041,42 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Proyecto Planta DOT</t>
+          <t>Proyecto Parque San Blas</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>1886468</t>
+          <t>1460619</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1886468&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1460619&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Decimoquinta</t>
+          <t>Tercera</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>1,300</t>
+          <t>60,900</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>26/12/2006</t>
+          <t>26/05/2006</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Aprobado</t>
+          <t>Desistido</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -21081,12 +21086,12 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Instalaciones fabriles sobre 2000 KVA</t>
+          <t>Centrales generadoras de energía mayores a 3 MW</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>QUIBORAX S.A.</t>
+          <t>Acciona Energía Chile SpA</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -21098,37 +21103,37 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Proyecto de Prospección Minera Vicuña, Sector Cerro Blanco, III Región</t>
+          <t>Proyecto Planta DOT</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>3035788</t>
+          <t>1886468</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=3035788&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=1886468&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Tercera</t>
+          <t>Decimoquinta</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>2,744</t>
+          <t>1,300</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>18/07/2008</t>
+          <t>26/12/2006</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -21143,12 +21148,12 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Proyecto de desarrollo minero sobre 5000 tons/mens</t>
+          <t>Instalaciones fabriles sobre 2000 KVA</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Minera Frontera del Oro SpA</t>
+          <t>QUIBORAX S.A.</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -21160,37 +21165,37 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Oleoducto de Central Termoeléctrica Quintero</t>
+          <t>Proyecto de Prospección Minera Vicuña, Sector Cerro Blanco, III Región</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>3410313</t>
+          <t>3035788</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=3410313&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=3035788&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Tercera</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>0,790</t>
+          <t>2,744</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>12/12/2008</t>
+          <t>18/07/2008</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -21205,59 +21210,54 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Oleoductos</t>
+          <t>Proyecto de desarrollo minero sobre 5000 tons/mens</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Enel Generación Chile S.A</t>
+          <t>Minera Frontera del Oro SpA</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>Geobiota</t>
-        </is>
-      </c>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>Carlos Prado</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Línea de Transmisión 1X110 kV, Planta Fotovoltaica Usya a Parque Eólico Valle de los Vientos</t>
+          <t>Oleoducto de Central Termoeléctrica Quintero</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2130151186</t>
+          <t>3410313</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2130151186&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=3410313&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2,607</t>
+          <t>0,790</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>16/01/2015</t>
+          <t>12/12/2008</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -21272,12 +21272,12 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Líneas de transmisión eléctrica de alto voltaje</t>
+          <t>Oleoductos</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>USYA SpA</t>
+          <t>Enel Generación Chile S.A</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -21287,34 +21287,29 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Félix Hidalgo Reyes</t>
-        </is>
-      </c>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>El presente documento, conforme lo dispone el artículo 2, letra f) de la Ley N° 19.300, corresponde al “documento descriptivo de una actividad o proyecto que se pretende realizar, o de las modificaciones que se le introducirán, otorgado bajo juramento por el respectivo titular, cuyo contenido permite al organismo competente evaluar si su impacto ambiental se ajusta a las normas ambientales vigentes ”, para cuyos efectos se describe y caracteriza el proyecto “Línea de Transmisión 1X110 kV, Planta Fotovoltaica Usya a Parque Eólico Valle de los Vientos” (en adelante el Proyecto), perteneciente a la empresa Acciona Energía Chile SpA. (en adelante el Titular), ubicado en la región de Antofagasta, provincia del Loa, comuna de Calama. El proyecto Línea de Transmisión 1X110 kV, Planta Fotovoltaica Usya a Parque Eólico Valle de los Vientos, consiste en la construcción y operación de una línea eléctrica de transmisión simple, la cual permitirá incorporar al Sistema Interconectado del Norte Grande (SING) la energía eléctrica proveniente del proyecto “Planta Fotovoltaica Usya”, en la subestación eléctrica Valle de los Vientos, existente y propiedad del Parque Eólico Valle de Los Vientos SpA. Específicamente se trata de una línea de transmisión de un circuito de 110kV, conformada por 16 estructuras de hormigón (postes) y de 2,3 km de longitud, y de la construcción de las obras civiles y eléctricas asociadas a la edificación de un paño de línea de tipo AIS (Air Insulated Subestation), en una superficie contigua a la Subestación Valle de los Vientos. Al respecto, cabe destacar que los proyectos, “Planta Fotovoltaica Usya” y “SE Valle de los Vientos”, se encuentran aprobados mediante Resolución de Calificación Ambiental (RCA) N°075/2013 y (RCA) N°0138/2010, respectivamente, y no requieren modificación alguna producto de la ejecución y operación del presente Proyecto. Objetivo El Proyecto tiene como objetivo transmitir la energía generada en la Planta Fotovoltaica Usya, consistente en 25 MW, hasta la SE Valle de los Vientos, permitiendo su posterior incorporación al Sistema Interconectado del Norte Grande (SING).</t>
+          <t>Carlos Prado</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Modificación de la línea de transmisión eléctrica del proyecto Parque Eólico Sierra Gorda Este</t>
+          <t>Línea de Transmisión 1X110 kV, Planta Fotovoltaica Usya a Parque Eólico Valle de los Vientos</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2132653801</t>
+          <t>2130151186</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2132653801&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2130151186&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -21324,12 +21319,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>2,607</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>23/08/2017</t>
+          <t>16/01/2015</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -21349,7 +21344,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Enel Green Power Chile S.A.</t>
+          <t>USYA SpA</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -21364,44 +21359,44 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>El Proyecto “Modificación de la línea de transmisión eléctrica del proyecto Parque Eólico Sierra Gorda Este” viene a modificar el trazado de la Línea de transmisión eléctrica (LTE) presentada dentro del Proyecto Parque Eólico Sierra Gorda Este (RCA N°490/2014) desde la estructura N° 114 hacia el Oeste, a fin de conectarse directamente con la S/E Sierra Gorda y contribuir a una optimización del Proyecto, dado que el diseño original contempla la conexión de la LTE del Parque Eólico Sierra Gorda Este con la LTE 1x220 kV Spence-Sierra Gorda. De esta forma, el Proyecto consiste principalmente en el cambio del trazado aprobado por la RCA Nº 490/2014 por el montaje de 19 estructuras para la extensión de la LTE y su correspondiente tendido eléctrico. Para el mencionado cambio de trazado, se realizarán actividades relacionadas a movimientos de tierra, construcción de fundaciones y malla puesta a tierra; montaje de estructuras, crucetas, aisladores, conductores y cable de guardia; para finalmente realizar el proceso de puesta en marcha para su conexión hasta la Subestación Eléctrica Sierra Gorda. Esta modificación considera un aumento de longitud referida a la LTE de 39 km a 42 km. Para acceder a las nuevas estructuras se habilitarán nuevos caminos derivados de la red de caminos existentes, cuyo propósito será atender las actividades asociadas a la construcción de las nuevas estructuras de la LTE y las posteriores visitas de inspección y verificación del estado de componentes que conforman la LTE. A continuación, se enumeran las modificaciones a realizar respecto del proyecto original: · Construcción/habilitación de 2,41 km de caminos de acceso a torres de LTE, y · Construcción de torres 115 a 133 e instalación de tendido eléctrico asociado a nuevo trazado LTE (torre 114 – S/E Sierra Gorda). Cabe destacar que la LTE, considera la modificación de la estructura N°114 para adecuarse al cambio de dirección que tendrá hacia la nueva estructura N°115 y finalmente con la Subestación Eléctrica Sierra Gorda. El tramo adicional tendrá una longitud de 2,7 km. En el Anexo 1.1 se muestra un plano con el detalle de la LTE a construir como parte del Proyecto y la conexión final a la S/E Sierra Gorda existente. Objetivo El Proyecto tiene como objetivo modificar el trazado de la Línea de transmisión eléctrica (LTE) presentada dentro del Proyecto Parque Eólico Sierra Gorda Este (RCA N°490/2014) desde la estructura N° 114 hacia el Oeste, a fin de conectarse directamente con la S/E Sierra Gorda y contribuir a una optimización del Proyecto.</t>
+          <t>El presente documento, conforme lo dispone el artículo 2, letra f) de la Ley N° 19.300, corresponde al “documento descriptivo de una actividad o proyecto que se pretende realizar, o de las modificaciones que se le introducirán, otorgado bajo juramento por el respectivo titular, cuyo contenido permite al organismo competente evaluar si su impacto ambiental se ajusta a las normas ambientales vigentes ”, para cuyos efectos se describe y caracteriza el proyecto “Línea de Transmisión 1X110 kV, Planta Fotovoltaica Usya a Parque Eólico Valle de los Vientos” (en adelante el Proyecto), perteneciente a la empresa Acciona Energía Chile SpA. (en adelante el Titular), ubicado en la región de Antofagasta, provincia del Loa, comuna de Calama. El proyecto Línea de Transmisión 1X110 kV, Planta Fotovoltaica Usya a Parque Eólico Valle de los Vientos, consiste en la construcción y operación de una línea eléctrica de transmisión simple, la cual permitirá incorporar al Sistema Interconectado del Norte Grande (SING) la energía eléctrica proveniente del proyecto “Planta Fotovoltaica Usya”, en la subestación eléctrica Valle de los Vientos, existente y propiedad del Parque Eólico Valle de Los Vientos SpA. Específicamente se trata de una línea de transmisión de un circuito de 110kV, conformada por 16 estructuras de hormigón (postes) y de 2,3 km de longitud, y de la construcción de las obras civiles y eléctricas asociadas a la edificación de un paño de línea de tipo AIS (Air Insulated Subestation), en una superficie contigua a la Subestación Valle de los Vientos. Al respecto, cabe destacar que los proyectos, “Planta Fotovoltaica Usya” y “SE Valle de los Vientos”, se encuentran aprobados mediante Resolución de Calificación Ambiental (RCA) N°075/2013 y (RCA) N°0138/2010, respectivamente, y no requieren modificación alguna producto de la ejecución y operación del presente Proyecto. Objetivo El Proyecto tiene como objetivo transmitir la energía generada en la Planta Fotovoltaica Usya, consistente en 25 MW, hasta la SE Valle de los Vientos, permitiendo su posterior incorporación al Sistema Interconectado del Norte Grande (SING).</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Modificación línea de transmisión Carrera Pinto ? Campos del Sol Sur Oeste</t>
+          <t>Modificación de la línea de transmisión eléctrica del proyecto Parque Eólico Sierra Gorda Este</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2141955128</t>
+          <t>2132653801</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2141955128&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2132653801&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Tercera</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>20/12/2018</t>
+          <t>23/08/2017</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -21436,44 +21431,44 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>El Proyecto “Modificación Línea de Transmisión Carrera Pinto – Campos del Sol Sur Oeste” viene a modificar el trazado de la Línea de transmisión eléctrica (LTE) presentada en el proyecto original (Línea de Transmisión Carrera Pinto - Campos del Sol Sur Oeste, RCA N°199/2016), tanto en su longitud como en su trazado, así como también en la incorporación de una Subestación Elevadora. De esta forma, el Proyecto consiste en el cambio del trazado aprobado por la RCA Nº 199/2016, aumentando el número de estructuras de 19 a 30, y aumentando la longitud de la LTE de 5,3 km a 7,43 km aproximadamente (2,13 km adicionales) además de la incorporación de la Subestación Elevadora, que reunirá toda la energía generada en el Parque Fotovoltaico Campos del Sol (proyecto con RCA aprobada N°214/2014). Para el mencionado cambio de trazado y aumento de longitud, se realizarán actividades relacionadas a movimientos de tierra, construcción de fundaciones y malla puesta a tierra; montaje de estructuras, crucetas, aisladores, conductores y cable de guardia. Por otro lado, para la construcción de la Subestación Elevadora se realizarán movimientos de tierra, construcción de fundaciones y malla de puesta a tierra y posterior implementación de la Subestación. Para acceder a las estructuras se habilitarán nuevos caminos derivados de la red de caminos existentes (C-17 y caminos internos existentes sin rol), cuyo propósito será atender las actividades asociadas a la construcción de estructuras de la LTE y la Subestación y las posteriores visitas de inspección y verificación del estado de componentes que conforman el Proyecto. A continuación, se enumeran las modificaciones a realizar respecto del proyecto original: · Reubicación de torres presentadas en el proyecto original (19 torres), · Construcción de 11 torres adicionales e instalación del tendido eléctrico, · Construcción/habilitación de caminos de acceso a torres de LTE y Subestación Elevadora, · Construcción de Subestación Elevadora. Objetivo El objetivo del Proyecto “Modificación Línea de Transmisión Carrera Pinto – Campos del Sol Sur Oeste” es realizar cambios al trazado de la Línea de transmisión eléctrica (LTE) Carrera Pinto - Campos del Sol Sur Oeste (RCA N°199/2016) e incorporar una Subestación Elevadora.</t>
+          <t>El Proyecto “Modificación de la línea de transmisión eléctrica del proyecto Parque Eólico Sierra Gorda Este” viene a modificar el trazado de la Línea de transmisión eléctrica (LTE) presentada dentro del Proyecto Parque Eólico Sierra Gorda Este (RCA N°490/2014) desde la estructura N° 114 hacia el Oeste, a fin de conectarse directamente con la S/E Sierra Gorda y contribuir a una optimización del Proyecto, dado que el diseño original contempla la conexión de la LTE del Parque Eólico Sierra Gorda Este con la LTE 1x220 kV Spence-Sierra Gorda. De esta forma, el Proyecto consiste principalmente en el cambio del trazado aprobado por la RCA Nº 490/2014 por el montaje de 19 estructuras para la extensión de la LTE y su correspondiente tendido eléctrico. Para el mencionado cambio de trazado, se realizarán actividades relacionadas a movimientos de tierra, construcción de fundaciones y malla puesta a tierra; montaje de estructuras, crucetas, aisladores, conductores y cable de guardia; para finalmente realizar el proceso de puesta en marcha para su conexión hasta la Subestación Eléctrica Sierra Gorda. Esta modificación considera un aumento de longitud referida a la LTE de 39 km a 42 km. Para acceder a las nuevas estructuras se habilitarán nuevos caminos derivados de la red de caminos existentes, cuyo propósito será atender las actividades asociadas a la construcción de las nuevas estructuras de la LTE y las posteriores visitas de inspección y verificación del estado de componentes que conforman la LTE. A continuación, se enumeran las modificaciones a realizar respecto del proyecto original: · Construcción/habilitación de 2,41 km de caminos de acceso a torres de LTE, y · Construcción de torres 115 a 133 e instalación de tendido eléctrico asociado a nuevo trazado LTE (torre 114 – S/E Sierra Gorda). Cabe destacar que la LTE, considera la modificación de la estructura N°114 para adecuarse al cambio de dirección que tendrá hacia la nueva estructura N°115 y finalmente con la Subestación Eléctrica Sierra Gorda. El tramo adicional tendrá una longitud de 2,7 km. En el Anexo 1.1 se muestra un plano con el detalle de la LTE a construir como parte del Proyecto y la conexión final a la S/E Sierra Gorda existente. Objetivo El Proyecto tiene como objetivo modificar el trazado de la Línea de transmisión eléctrica (LTE) presentada dentro del Proyecto Parque Eólico Sierra Gorda Este (RCA N°490/2014) desde la estructura N° 114 hacia el Oeste, a fin de conectarse directamente con la S/E Sierra Gorda y contribuir a una optimización del Proyecto.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Parque hibrido Amolanas</t>
+          <t>Modificación línea de transmisión Carrera Pinto ? Campos del Sol Sur Oeste</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2152937944</t>
+          <t>2141955128</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2152937944&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2141955128&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Cuarta</t>
+          <t>Tercera</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>340,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>23/08/2021</t>
+          <t>20/12/2018</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -21488,12 +21483,12 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Centrales generadoras de energía mayores a 3 MW</t>
+          <t>Líneas de transmisión eléctrica de alto voltaje</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>PACIFIC HYDRO CHILE S.A.</t>
+          <t>Enel Green Power Chile S.A.</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -21508,44 +21503,44 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>El Proyecto Parque Hibrido Amolanas, contempla la generación de energía eléctrica, por medio de un parque híbrido, el cual considera la construcción, implementación y funcionamiento de un parque eólico, y de un parque fotovoltaico, los cuales operarán en forma conjunta. A partir de éstos, la capacidad total de generación del proyecto será de 199,1 MW, de los cuales 117 MW se generarán a través del sistema eólico, y 82,1 MW se generarán a través del sistema fotovoltaico. Objetivo El Objetivo General del proyecto es la generación de energía eléctrica, por medio de un parque híbrido, el cual considera la construcción, implementación y funcionamiento de un parque eólico, y paralelamente de un parque fotovoltaico, los cuales operarán en forma conjunta.</t>
+          <t>El Proyecto “Modificación Línea de Transmisión Carrera Pinto – Campos del Sol Sur Oeste” viene a modificar el trazado de la Línea de transmisión eléctrica (LTE) presentada en el proyecto original (Línea de Transmisión Carrera Pinto - Campos del Sol Sur Oeste, RCA N°199/2016), tanto en su longitud como en su trazado, así como también en la incorporación de una Subestación Elevadora. De esta forma, el Proyecto consiste en el cambio del trazado aprobado por la RCA Nº 199/2016, aumentando el número de estructuras de 19 a 30, y aumentando la longitud de la LTE de 5,3 km a 7,43 km aproximadamente (2,13 km adicionales) además de la incorporación de la Subestación Elevadora, que reunirá toda la energía generada en el Parque Fotovoltaico Campos del Sol (proyecto con RCA aprobada N°214/2014). Para el mencionado cambio de trazado y aumento de longitud, se realizarán actividades relacionadas a movimientos de tierra, construcción de fundaciones y malla puesta a tierra; montaje de estructuras, crucetas, aisladores, conductores y cable de guardia. Por otro lado, para la construcción de la Subestación Elevadora se realizarán movimientos de tierra, construcción de fundaciones y malla de puesta a tierra y posterior implementación de la Subestación. Para acceder a las estructuras se habilitarán nuevos caminos derivados de la red de caminos existentes (C-17 y caminos internos existentes sin rol), cuyo propósito será atender las actividades asociadas a la construcción de estructuras de la LTE y la Subestación y las posteriores visitas de inspección y verificación del estado de componentes que conforman el Proyecto. A continuación, se enumeran las modificaciones a realizar respecto del proyecto original: · Reubicación de torres presentadas en el proyecto original (19 torres), · Construcción de 11 torres adicionales e instalación del tendido eléctrico, · Construcción/habilitación de caminos de acceso a torres de LTE y Subestación Elevadora, · Construcción de Subestación Elevadora. Objetivo El objetivo del Proyecto “Modificación Línea de Transmisión Carrera Pinto – Campos del Sol Sur Oeste” es realizar cambios al trazado de la Línea de transmisión eléctrica (LTE) Carrera Pinto - Campos del Sol Sur Oeste (RCA N°199/2016) e incorporar una Subestación Elevadora.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Nueva Línea 2x220 Nueva Alto Melipilla - Nueva Casablanca - La Pólvora - Agua Santa</t>
+          <t>Parque hibrido Amolanas</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2145591077</t>
+          <t>2152937944</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2145591077&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2152937944&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Interregional</t>
+          <t>Cuarta</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>50,499</t>
+          <t>340,000</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>05/02/2020</t>
+          <t>23/08/2021</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -21555,17 +21550,17 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>Estudio de Impacto Ambiental</t>
+          <t>Declaración de Impacto Ambiental</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Líneas de transmisión eléctrica de alto voltaje</t>
+          <t>Centrales generadoras de energía mayores a 3 MW</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Casablanca Transmisora de Energía S.A.</t>
+          <t>PACIFIC HYDRO CHILE S.A.</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -21580,44 +21575,44 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>El proyecto “Nueva Línea 2x220 Nueva Alto Melipilla - Nueva Casablanca - La Pólvora - Agua Santa” (en adelante “el Proyecto”), consiste en la construcción de una línea de transmisión eléctrica (LTE) de doble circuito, una tensión de 220 kV y 106,84 km de longitud, extendiéndose desde la comuna de Melipilla hasta la comuna de Viña del Mar. Asimismo, el proyecto contempla la construcción de la subestación eléctrica (S/E) Nueva Casablanca 220/66 kV, la conexión con cuatro (4) S/E existentes: Nueva Alto Melipilla 220 kV; Casablanca 66 kV; Agua Santa 220 kV; y con la S/E La Pólvora 220/110 kV (esta última siendo de propiedad del titular, y actualmente terminando su proceso de evaluación bajo el nombre de DIA “Nueva Subestación La Pólvora 220/110 kV”). Además, contempla la construcción de un Enlace en doble circuito de 672 metros, en una tensión de 66 kV para conectar la S/E Nueva Casablanca con la S/E Casablanca (existente). Objetivo El presente Proyecto nace en el marco de ejecución del listado de las instalaciones de Transmisión Zonal de Ejecución Obligatoria, establecido por el Ministerio de Energía el 19 de agosto de 2017 mediante el Decreto N°418 Exento del Ministerio de Energía, de fecha 19 de agosto de 2017, con el objetivo de robustecer la red de transmisión nacional.</t>
+          <t>El Proyecto Parque Hibrido Amolanas, contempla la generación de energía eléctrica, por medio de un parque híbrido, el cual considera la construcción, implementación y funcionamiento de un parque eólico, y de un parque fotovoltaico, los cuales operarán en forma conjunta. A partir de éstos, la capacidad total de generación del proyecto será de 199,1 MW, de los cuales 117 MW se generarán a través del sistema eólico, y 82,1 MW se generarán a través del sistema fotovoltaico. Objetivo El Objetivo General del proyecto es la generación de energía eléctrica, por medio de un parque híbrido, el cual considera la construcción, implementación y funcionamiento de un parque eólico, y paralelamente de un parque fotovoltaico, los cuales operarán en forma conjunta.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Plan de Reducción de Extracciones en el Salar de Atacama</t>
+          <t>Nueva Línea 2x220 Nueva Alto Melipilla - Nueva Casablanca - La Pólvora - Agua Santa</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2154490427</t>
+          <t>2145591077</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2154490427&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2145591077&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Interregional</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>0,778</t>
+          <t>50,499</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>31/01/2022</t>
+          <t>05/02/2020</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -21632,12 +21627,12 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Ejecución de obras, programas o actividades en parques nacionales, reservas nacionales, monumentos naturales, reservas de zonas vírgenes, santuarios de la naturaleza, parques marinos, reservas marinas o en cualesquiera otra área colocada bajo protección oficial, en los casos en que la legislación respectiva lo permita</t>
+          <t>Líneas de transmisión eléctrica de alto voltaje</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Nova Andino Litio SpA</t>
+          <t>Casablanca Transmisora de Energía S.A.</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -21647,34 +21642,34 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Ingrid Mariela Zelaya Lathan</t>
+          <t>Félix Hidalgo Reyes</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>El Proyecto “Plan de Reducción de Extracciones en el Salar de Atacama” tiene por objeto reducir la cantidad máxima de salmuera a bombear desde las zonas de extracción autorizadas en el núcleo del Salar y de agua a extraer desde pozos ubicados en la zona aluvial en el margen este del Salar; implementar ajustes en el plan de seguimiento ambiental y en los planes de alerta temprana, y adoptar medidas asociadas a la pérdida de ejemplares de Algarrobo en el sector del pozo Camar-2. Las reducciones en el bombeo de salmuera y agua consisten en la reducción progresiva de la extracción de salmuera que se realiza desde las zonas autorizadas en el núcleo del Salar (sectores MOP y SOP), alcanzando un bombeo promedio anual máximo de 822 l/s al año 2028, y en la limitación de la extracción de agua a un máximo total de 120 l/s a extraer en conjunto desde los pozos Mullay-1, Allana-1, Socaire-5 y CA-2015, a partir de la aprobación del Proyecto. Estas reducciones de bombeo, que se someten al Sistema de Evaluación de Impacto Ambiental sin considerar una ampliación de la vida útil de la operación, implican una disminución sustantiva de los límites máximos actualmente autorizados en la RCA N°226/2006 hasta el año 2030. Adicional a las reducciones de extracciones, planteadas en el Plan de Desarrollo Sustentable de SQM (2020) e incorporadas como compromiso en el Programa de Cumplimiento propuesto en el procedimiento sancionatorio F-041-2016 de la Superintendencia del Medio Ambiente, el Proyecto considera las siguientes materias igualmente comprometidas en el programa de cumplimiento: • Actualización de los Planes de Alerta Temprana (PAT) aplicables a los sistemas Soncor, Aguas de Quelana, Peine y Vegetación Borde Este. • Actualización del Plan de Seguimiento Ambiental (PSA), tanto hidrogeológico (PSAH) como biótico (PSAB) • Plan de medidas asociados a la pérdida de ejemplares de Algarrobo presentes en el sector del pozo Camar-2, objeto de seguimiento conforme a la RCA N°226/2006, incluyendo la reforestación de algarrobos. El Proyecto corresponde a una modificación de proyecto existente, calificado favorablemente mediante RCA N°226/2006, que calificó el proyecto “Cambios y Mejoras de la Operación Minera en el Salar de Atacama”. El Proyecto no considera ningún otro cambio, ajuste o modificación en la operación minera de SQM Salar S.A. en el Salar de Atacama. Objetivo El Proyecto “Plan de Reducción de Extracciones en el Salar de Atacama” tiene por objeto reducir la cantidad máxima de salmuera a bombear desde las zonas de extracción autorizadas en el núcleo del Salar y de agua a extraer desde pozos ubicados en la zona aluvial en el margen este del Salar; implementar ajustes en el plan de seguimiento ambiental y en los planes de alerta temprana, y adoptar medidas asociadas a la pérdida de ejemplares de Algarrobo en el sector del pozo Camar-2. Los objetivos específicos del Proyecto son: · Disminuir progresivamente la extracción de salmuera hasta llegar a 822 l/s el año 2028 y hasta el término de la vida útil de la operación autorizada mediante RCA N°226/2006. · Disminuir en un 50% la cantidad máxima total de agua a extraer respecto de lo autorizado por la RCA N°226/2006. · Actualizar el Plan de Seguimiento Ambiental hidrogeológico y biótico (PSAH y PSAB). · Actualizar los Planes de Alerta Temprana (PAT) · Implementar medidas para hacerse cargo de la afectación progresiva del estado de vitalidad de algarrobos en el área del pozo Camar-2.</t>
+          <t>El proyecto “Nueva Línea 2x220 Nueva Alto Melipilla - Nueva Casablanca - La Pólvora - Agua Santa” (en adelante “el Proyecto”), consiste en la construcción de una línea de transmisión eléctrica (LTE) de doble circuito, una tensión de 220 kV y 106,84 km de longitud, extendiéndose desde la comuna de Melipilla hasta la comuna de Viña del Mar. Asimismo, el proyecto contempla la construcción de la subestación eléctrica (S/E) Nueva Casablanca 220/66 kV, la conexión con cuatro (4) S/E existentes: Nueva Alto Melipilla 220 kV; Casablanca 66 kV; Agua Santa 220 kV; y con la S/E La Pólvora 220/110 kV (esta última siendo de propiedad del titular, y actualmente terminando su proceso de evaluación bajo el nombre de DIA “Nueva Subestación La Pólvora 220/110 kV”). Además, contempla la construcción de un Enlace en doble circuito de 672 metros, en una tensión de 66 kV para conectar la S/E Nueva Casablanca con la S/E Casablanca (existente). Objetivo El presente Proyecto nace en el marco de ejecución del listado de las instalaciones de Transmisión Zonal de Ejecución Obligatoria, establecido por el Ministerio de Energía el 19 de agosto de 2017 mediante el Decreto N°418 Exento del Ministerio de Energía, de fecha 19 de agosto de 2017, con el objetivo de robustecer la red de transmisión nacional.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Nueva Subestación Eléctrica Seccionadora Llullaillaco y Línea de Seccionamiento, Ruta 5 Norte Km 1.207</t>
+          <t>Plan de Reducción de Extracciones en el Salar de Atacama</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2162750184</t>
+          <t>2154490427</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2162750184&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2154490427&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -21684,32 +21679,32 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>0,778</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>06/09/2024</t>
+          <t>31/01/2022</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Desistido</t>
+          <t>Aprobado</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Declaración de Impacto Ambiental</t>
+          <t>Estudio de Impacto Ambiental</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Subestaciones</t>
+          <t>Ejecución de obras, programas o actividades en parques nacionales, reservas nacionales, monumentos naturales, reservas de zonas vírgenes, santuarios de la naturaleza, parques marinos, reservas marinas o en cualesquiera otra área colocada bajo protección oficial, en los casos en que la legislación respectiva lo permita</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Colbún S.A.</t>
+          <t>Nova Andino Litio SpA</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -21724,14 +21719,14 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>El Proyecto “Nueva Subestación Eléctrica Seccionadora Llullaillaco y Línea de Seccionamiento, Ruta 5 Norte Km 1.207” consiste en la construcción de una subestación seccionadora, denominada Llullaillaco, la cual seccionará la línea existente 2x500 kV Parinas – Cumbre, con sus respectivos paños de línea y patio en 500 kV. La subestación proyecta su construcción en la comuna Taltal, provincia de Antofagasta, Región de Antofagasta, y tiene por objetivo principal aumentar la capacidad de transportar energía y de la trasformación del sistema de transmisión en la Región. El Proyecto contempla una fase de construcción de 16 meses aproximadamente para lo cual habilitará una instalación de faenas en una superficie total de 2 ha, la cual contará con instalaciones temporales tales como oficinas, bodegas de almacenamiento de insumos, materiales y residuos, servicios higiénicos, zona de estacionamiento, entre otras obras. Como parte de las obras proyectadas y que serán de carácter permanente, se considera la habilitación de un camino de acceso para construcción y operación que unirá la Ruta 5 con la subestación en una longitud de 450 m. También contempla la construcción de 400 m aproximadamente de una línea de alta tensión que permitirá el seccionamiento de la línea existente y conexión a la subestación seccionadora en patio de 500 kV. C onsiderará además la nivelación de un terreno de 3,6 ha para tres futuros bancos de autotransformadores 500/220 kV y espacio para un patio de 220 kV, de acuerdo a lo declarado en los Decretos Exentos N° 257/2022 y N° 229/2021 del Ministerio de Energía . Las obras se proyectan en un predio de aproximadamente 48 ha, no obstante, la superficie edificable se proyecta en un área de 1,9 ha aproximadamente. El Proyecto contempla una vida útil mínima de 40 años, no obstante producto de los recambios de equipos posibles, mejoras tecnológicas, entre otras, se espera que el Proyecto pueda tener una vida útil indefinida. Objetivo El objetivo del proyecto "Nueva Subestación Eléctrica Seccionadora Llullaillaco y Línea de Seccionamiento, Ruta 5 Norte Km 1.207” es aumentar la capacidad de transportar energía y de la trasformación del sistema de transmisión en la Región de Antofagasta, la cual permita aprovechar las bondades de la zona definida para fines de generación eléctrica en base a fuentes renovables y en el caso particular de este proyecto mediante la ampliación de la actual infraestructura eléctrica para el fortalecimiento del sistema de transmisión, en consistencia con lo dispuesto en los Decretos Exentos N° 257/2022 y N° 229/2021 del Ministerio de Energía.</t>
+          <t>El Proyecto “Plan de Reducción de Extracciones en el Salar de Atacama” tiene por objeto reducir la cantidad máxima de salmuera a bombear desde las zonas de extracción autorizadas en el núcleo del Salar y de agua a extraer desde pozos ubicados en la zona aluvial en el margen este del Salar; implementar ajustes en el plan de seguimiento ambiental y en los planes de alerta temprana, y adoptar medidas asociadas a la pérdida de ejemplares de Algarrobo en el sector del pozo Camar-2. Las reducciones en el bombeo de salmuera y agua consisten en la reducción progresiva de la extracción de salmuera que se realiza desde las zonas autorizadas en el núcleo del Salar (sectores MOP y SOP), alcanzando un bombeo promedio anual máximo de 822 l/s al año 2028, y en la limitación de la extracción de agua a un máximo total de 120 l/s a extraer en conjunto desde los pozos Mullay-1, Allana-1, Socaire-5 y CA-2015, a partir de la aprobación del Proyecto. Estas reducciones de bombeo, que se someten al Sistema de Evaluación de Impacto Ambiental sin considerar una ampliación de la vida útil de la operación, implican una disminución sustantiva de los límites máximos actualmente autorizados en la RCA N°226/2006 hasta el año 2030. Adicional a las reducciones de extracciones, planteadas en el Plan de Desarrollo Sustentable de SQM (2020) e incorporadas como compromiso en el Programa de Cumplimiento propuesto en el procedimiento sancionatorio F-041-2016 de la Superintendencia del Medio Ambiente, el Proyecto considera las siguientes materias igualmente comprometidas en el programa de cumplimiento: • Actualización de los Planes de Alerta Temprana (PAT) aplicables a los sistemas Soncor, Aguas de Quelana, Peine y Vegetación Borde Este. • Actualización del Plan de Seguimiento Ambiental (PSA), tanto hidrogeológico (PSAH) como biótico (PSAB) • Plan de medidas asociados a la pérdida de ejemplares de Algarrobo presentes en el sector del pozo Camar-2, objeto de seguimiento conforme a la RCA N°226/2006, incluyendo la reforestación de algarrobos. El Proyecto corresponde a una modificación de proyecto existente, calificado favorablemente mediante RCA N°226/2006, que calificó el proyecto “Cambios y Mejoras de la Operación Minera en el Salar de Atacama”. El Proyecto no considera ningún otro cambio, ajuste o modificación en la operación minera de SQM Salar S.A. en el Salar de Atacama. Objetivo El Proyecto “Plan de Reducción de Extracciones en el Salar de Atacama” tiene por objeto reducir la cantidad máxima de salmuera a bombear desde las zonas de extracción autorizadas en el núcleo del Salar y de agua a extraer desde pozos ubicados en la zona aluvial en el margen este del Salar; implementar ajustes en el plan de seguimiento ambiental y en los planes de alerta temprana, y adoptar medidas asociadas a la pérdida de ejemplares de Algarrobo en el sector del pozo Camar-2. Los objetivos específicos del Proyecto son: · Disminuir progresivamente la extracción de salmuera hasta llegar a 822 l/s el año 2028 y hasta el término de la vida útil de la operación autorizada mediante RCA N°226/2006. · Disminuir en un 50% la cantidad máxima total de agua a extraer respecto de lo autorizado por la RCA N°226/2006. · Actualizar el Plan de Seguimiento Ambiental hidrogeológico y biótico (PSAH y PSAB). · Actualizar los Planes de Alerta Temprana (PAT) · Implementar medidas para hacerse cargo de la afectación progresiva del estado de vitalidad de algarrobos en el área del pozo Camar-2.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -21741,12 +21736,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2163217753</t>
+          <t>2162750184</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2163217753&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2162750184&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -21761,12 +21756,12 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>12/09/2024</t>
+          <t>06/09/2024</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Aprobado</t>
+          <t>Desistido</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -21796,44 +21791,44 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>El Proyecto “Nueva Subestación Eléctrica Seccionadora Llullaillaco y Línea de Seccionamiento, Ruta 5 Norte Km 1.207” consiste en la construcción de una subestación seccionadora, denominada Llullaillaco, la cual seccionará la línea existente 2x500 kV Parinas – Cumbre, con sus respectivos paños de línea y patio en 500 kV. La subestación proyecta su construcción en la comuna Taltal, provincia de Antofagasta, Región de Antofagasta, y tiene por objetivo principal aumentar la capacidad de transportar energía y de la trasformación del sistema de transmisión en la Región. El Proyecto contempla una fase de construcción de 16 meses aproximadamente para lo cual habilitará una instalación de faenas en una superficie total de 2 ha, la cual contará con instalaciones temporales tales como oficinas, bodegas de almacenamiento de insumos, materiales y residuos, servicios higiénicos, zona de estacionamiento, entre otras obras. Como parte de las obras proyectadas y que serán de carácter permanente, se considera la habilitación de un camino de acceso para construcción y operación que unirá la Ruta 5 con la subestación en una longitud de 450 m. También contempla la construcción de 400 m aproximadamente de una línea de alta tensión que permitirá el seccionamiento de la línea existente y conexión a la subestación seccionadora en patio de 500 kV. Considerará además la nivelación de un terreno de 3,6 ha para tres futuros bancos de autotransformadores 500/220 kV y espacio para un patio de 220 kV, de acuerdo a lo declarado en los Decretos Exentos N° 257/2022 y N° 229/2021 del Ministerio de Energía. Las obras se proyectan en un predio de aproximadamente 48 ha, no obstante, la superficie edificable se proyecta en un área de 1,9 ha aproximadamente. El Proyecto contempla una vida útil mínima de 40 años, no obstante producto de los recambios de equipos posibles, mejoras tecnológicas, entre otras, se espera que el Proyecto pueda tener una vida útil indefinida. Objetivo El objetivo del proyecto "Nueva Subestación Eléctrica Seccionadora Llullaillaco y Línea de Seccionamiento, Ruta 5 Norte Km 1.207” es aumentar la capacidad de transportar energía y de la trasformación del sistema de transmisión en la Región de Antofagasta, la cual permita aprovechar las bondades de la zona definida para fines de generación eléctrica en base a fuentes renovables y en el caso particular de este proyecto mediante la ampliación de la actual infraestructura eléctrica para el fortalecimiento del sistema de transmisión, en consistencia con lo dispuesto en los Decretos Exentos N° 257/2022 y N° 229/2021 del Ministerio de Energía.</t>
+          <t>El Proyecto “Nueva Subestación Eléctrica Seccionadora Llullaillaco y Línea de Seccionamiento, Ruta 5 Norte Km 1.207” consiste en la construcción de una subestación seccionadora, denominada Llullaillaco, la cual seccionará la línea existente 2x500 kV Parinas – Cumbre, con sus respectivos paños de línea y patio en 500 kV. La subestación proyecta su construcción en la comuna Taltal, provincia de Antofagasta, Región de Antofagasta, y tiene por objetivo principal aumentar la capacidad de transportar energía y de la trasformación del sistema de transmisión en la Región. El Proyecto contempla una fase de construcción de 16 meses aproximadamente para lo cual habilitará una instalación de faenas en una superficie total de 2 ha, la cual contará con instalaciones temporales tales como oficinas, bodegas de almacenamiento de insumos, materiales y residuos, servicios higiénicos, zona de estacionamiento, entre otras obras. Como parte de las obras proyectadas y que serán de carácter permanente, se considera la habilitación de un camino de acceso para construcción y operación que unirá la Ruta 5 con la subestación en una longitud de 450 m. También contempla la construcción de 400 m aproximadamente de una línea de alta tensión que permitirá el seccionamiento de la línea existente y conexión a la subestación seccionadora en patio de 500 kV. C onsiderará además la nivelación de un terreno de 3,6 ha para tres futuros bancos de autotransformadores 500/220 kV y espacio para un patio de 220 kV, de acuerdo a lo declarado en los Decretos Exentos N° 257/2022 y N° 229/2021 del Ministerio de Energía . Las obras se proyectan en un predio de aproximadamente 48 ha, no obstante, la superficie edificable se proyecta en un área de 1,9 ha aproximadamente. El Proyecto contempla una vida útil mínima de 40 años, no obstante producto de los recambios de equipos posibles, mejoras tecnológicas, entre otras, se espera que el Proyecto pueda tener una vida útil indefinida. Objetivo El objetivo del proyecto "Nueva Subestación Eléctrica Seccionadora Llullaillaco y Línea de Seccionamiento, Ruta 5 Norte Km 1.207” es aumentar la capacidad de transportar energía y de la trasformación del sistema de transmisión en la Región de Antofagasta, la cual permita aprovechar las bondades de la zona definida para fines de generación eléctrica en base a fuentes renovables y en el caso particular de este proyecto mediante la ampliación de la actual infraestructura eléctrica para el fortalecimiento del sistema de transmisión, en consistencia con lo dispuesto en los Decretos Exentos N° 257/2022 y N° 229/2021 del Ministerio de Energía.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Planta de Combustibles Sintéticos Cabo Negro</t>
+          <t>Nueva Subestación Eléctrica Seccionadora Llullaillaco y Línea de Seccionamiento, Ruta 5 Norte Km 1.207</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2160078437</t>
+          <t>2163217753</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2160078437&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2163217753&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Duodécima</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>830,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>16/10/2023</t>
+          <t>12/09/2024</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -21843,17 +21838,17 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Estudio de Impacto Ambiental</t>
+          <t>Declaración de Impacto Ambiental</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Instalaciones fabriles sobre 2.000 KVA</t>
+          <t>Subestaciones</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>HIF CHILE 1 SpA</t>
+          <t>Colbún S.A.</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -21868,29 +21863,29 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>El Proyecto “ Planta de combustibles carbono neutral Cabo Negro” consiste en la construcción y operación de una planta química de e-Combustibles para la producción de e-Metanol (CH 3 OH), e-Gasolina y e-GL (gas licuado). La planta se emplazará en la comuna de Punta Arenas, Región de Magallanes y de la Antártica Chilena, en una superficie aproximada de 57,97 ha. La planta de e-Combustibles considera una capacidad de producción máxima de 173.600 ton/año de e-Metanol, el cual según definición comercial podrá ser exportado directamente como e-Metanol, o bien, ser convertido total o parcialmente a e-Gasolina y e-GL alcanzando una producción máxima de 70.000 ton/año de e-Gasolina y 8.030 ton/año de e-GL, en el caso de que el 100% de e-Metanol sea transformado. Se estima una tasa máxima de 792 ton/día de e-Metanol, de 37 ton/día de e-GL de 320 ton/día de e-Gasolina. Cabe señalar que para la estimación de la producción anual se considera el 60% de la proyección anual de la tasa máxima diaria de producción de e-Metanol. La síntesis de e-Metanol se realiza a partir de la mezcla de hidrógeno (H 2 ), generado a través de la electrólisis de agua desmineralizada (obtenida previamente mediante captación de agua de mar y la recirculación de aguas residuales tratadas), y de dióxido de carbono (CO 2 ), para el cual se consideran tres (3) opciones complementarias (o de respaldo) de obtención: 1) conversión de biomasa, 2) captación de dióxido de carbono (CO 2 ) del aire y 3) importación marítima de dióxido de carbono (CO 2 ) criogénico. Cabe aclarar que la mayor parte del agua desmineralizada que será suministrada a la planta de e-Combustibles corresponderá a agua de proceso tratada, mientras solamente una parte menor provendrá de la captación de agua de mar. De la mezcla del hidrógeno (H 2 ) con el dióxido de carbono (CO 2 ), se obtiene e-Metanol crudo, el cual es sometido a un proceso de destilación para obtener un e-Metanol grado AA con valor comercial, el cual es almacenado y posteriormente conducido para su exportación y/o conversión a e-Gasolina y e-GL. La conversión de e-Metanol a e-Gasolina y e-GL tendrá lugar en la planta de e-Metanol a e-Gasolina (MtG por sus siglas en inglés), la cual estará compuesta por 2 unidades productoras, cada una equipada con un reactor para la conversión de e-Metanol a e-Gasolina, un fraccionador para la separación de la e-Gasolina liviana de la fracción pesada y una unidad de hidrotratamiento para cortar los hidrocarburos de cadena larga e hidrogenar los hidrocarburos insaturados. Tanto el e-Metanol como la e-Gasolina serán conducidos mediante tuberías hasta el Terminal de Cabo Negro para su exportación, en tanto el e-GL será transportado a través de tractocamiones hacia Puerto Mardones o el destino que corresponda. Objetivo El objetivo del Proyecto es la producción de e-Metanol, e-Gasolina y e-GL como combustible carbono neutral a partir de energía eólica, agua de mar, agua de proceso recirculada y captura de CO 2 del aire y/o fuentes biogénicas.</t>
+          <t>El Proyecto “Nueva Subestación Eléctrica Seccionadora Llullaillaco y Línea de Seccionamiento, Ruta 5 Norte Km 1.207” consiste en la construcción de una subestación seccionadora, denominada Llullaillaco, la cual seccionará la línea existente 2x500 kV Parinas – Cumbre, con sus respectivos paños de línea y patio en 500 kV. La subestación proyecta su construcción en la comuna Taltal, provincia de Antofagasta, Región de Antofagasta, y tiene por objetivo principal aumentar la capacidad de transportar energía y de la trasformación del sistema de transmisión en la Región. El Proyecto contempla una fase de construcción de 16 meses aproximadamente para lo cual habilitará una instalación de faenas en una superficie total de 2 ha, la cual contará con instalaciones temporales tales como oficinas, bodegas de almacenamiento de insumos, materiales y residuos, servicios higiénicos, zona de estacionamiento, entre otras obras. Como parte de las obras proyectadas y que serán de carácter permanente, se considera la habilitación de un camino de acceso para construcción y operación que unirá la Ruta 5 con la subestación en una longitud de 450 m. También contempla la construcción de 400 m aproximadamente de una línea de alta tensión que permitirá el seccionamiento de la línea existente y conexión a la subestación seccionadora en patio de 500 kV. Considerará además la nivelación de un terreno de 3,6 ha para tres futuros bancos de autotransformadores 500/220 kV y espacio para un patio de 220 kV, de acuerdo a lo declarado en los Decretos Exentos N° 257/2022 y N° 229/2021 del Ministerio de Energía. Las obras se proyectan en un predio de aproximadamente 48 ha, no obstante, la superficie edificable se proyecta en un área de 1,9 ha aproximadamente. El Proyecto contempla una vida útil mínima de 40 años, no obstante producto de los recambios de equipos posibles, mejoras tecnológicas, entre otras, se espera que el Proyecto pueda tener una vida útil indefinida. Objetivo El objetivo del proyecto "Nueva Subestación Eléctrica Seccionadora Llullaillaco y Línea de Seccionamiento, Ruta 5 Norte Km 1.207” es aumentar la capacidad de transportar energía y de la trasformación del sistema de transmisión en la Región de Antofagasta, la cual permita aprovechar las bondades de la zona definida para fines de generación eléctrica en base a fuentes renovables y en el caso particular de este proyecto mediante la ampliación de la actual infraestructura eléctrica para el fortalecimiento del sistema de transmisión, en consistencia con lo dispuesto en los Decretos Exentos N° 257/2022 y N° 229/2021 del Ministerio de Energía.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Parque Eólico Faro del Sur</t>
+          <t>Planta de Combustibles Sintéticos Cabo Negro</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2160813317</t>
+          <t>2160078437</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2160813317&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2160078437&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -21900,12 +21895,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>22/12/2023</t>
+          <t>16/10/2023</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -21920,12 +21915,12 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Centrales generadoras de energía mayores a 3 MW</t>
+          <t>Instalaciones fabriles sobre 2.000 KVA</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Eólica Faro del Sur S.P.A</t>
+          <t>HIF CHILE 1 SpA</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -21935,49 +21930,49 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Félix Hidalgo Reyes</t>
+          <t>Ingrid Mariela Zelaya Lathan</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>El Proyecto “Parque Eólico Faro del Sur” consiste en la construcción y operación de un parque eólico, en la comuna de Punta Arenas, Región de Magallanes y de la Antártica Chilena, con una potencia nominal de 384 MW y una vida útil proyectada de 29 años. El Parque Eólico está conformado por 64 aerogeneradores de tres palas, que se distribuirán en una superficie predial total de 3.791 hectáreas aproximadamente. Cada aerogenerador ocupará una superficie en promedio de 657,17 m2, tendrá una altura total de 200 m, y estará compuesto por una torre de 115 m de altura de buje y un rotor de 170 m de diámetro. El parque contará con una subestación elevadora de 33 kV a 66 kV en una superficie de 2,52 ha, donde se agruparán los circuitos internos y desde donde la energía será evacuada a través de una línea de transmisión de 66 kV, hasta una subestación reductora de 66 kV a 33 kV en una superficie de 0,45 ha. La Línea de Transmisión tendrá una longitud de aproximadamente 12,274 km y una superficie de 7,61 ha, la cual se extenderá de forma subterránea desde el Parque Eólico hasta el punto de entrega final en la Planta para la Producción de Combustibles Carbono Neutral (e-Combustibles) en el sector de Cabo Negro que se encuentra actualmente en evaluación. Adicionalmente, el Proyecto contará con instalaciones para la operación y seguridad del Parque Eólico tales como edificio de operación y mantenimiento, salas eléctricas, bodegas, oficinas, las que se emplazarán en el polígono destinado a la subestación elevadora. Objetivo El objetivo del Proyecto es la construcción y operación de un parque eólico de generación eléctrica de una potencia nominal de 384 MW, y la construcción y operación de una Línea de Transmisión de la energía producida, que permitirá aprovechar el recurso eólico de la Región de Magallanes y de la Antártica Chilena para generar energía limpia y sustentable.</t>
+          <t>El Proyecto “ Planta de combustibles carbono neutral Cabo Negro” consiste en la construcción y operación de una planta química de e-Combustibles para la producción de e-Metanol (CH 3 OH), e-Gasolina y e-GL (gas licuado). La planta se emplazará en la comuna de Punta Arenas, Región de Magallanes y de la Antártica Chilena, en una superficie aproximada de 57,97 ha. La planta de e-Combustibles considera una capacidad de producción máxima de 173.600 ton/año de e-Metanol, el cual según definición comercial podrá ser exportado directamente como e-Metanol, o bien, ser convertido total o parcialmente a e-Gasolina y e-GL alcanzando una producción máxima de 70.000 ton/año de e-Gasolina y 8.030 ton/año de e-GL, en el caso de que el 100% de e-Metanol sea transformado. Se estima una tasa máxima de 792 ton/día de e-Metanol, de 37 ton/día de e-GL de 320 ton/día de e-Gasolina. Cabe señalar que para la estimación de la producción anual se considera el 60% de la proyección anual de la tasa máxima diaria de producción de e-Metanol. La síntesis de e-Metanol se realiza a partir de la mezcla de hidrógeno (H 2 ), generado a través de la electrólisis de agua desmineralizada (obtenida previamente mediante captación de agua de mar y la recirculación de aguas residuales tratadas), y de dióxido de carbono (CO 2 ), para el cual se consideran tres (3) opciones complementarias (o de respaldo) de obtención: 1) conversión de biomasa, 2) captación de dióxido de carbono (CO 2 ) del aire y 3) importación marítima de dióxido de carbono (CO 2 ) criogénico. Cabe aclarar que la mayor parte del agua desmineralizada que será suministrada a la planta de e-Combustibles corresponderá a agua de proceso tratada, mientras solamente una parte menor provendrá de la captación de agua de mar. De la mezcla del hidrógeno (H 2 ) con el dióxido de carbono (CO 2 ), se obtiene e-Metanol crudo, el cual es sometido a un proceso de destilación para obtener un e-Metanol grado AA con valor comercial, el cual es almacenado y posteriormente conducido para su exportación y/o conversión a e-Gasolina y e-GL. La conversión de e-Metanol a e-Gasolina y e-GL tendrá lugar en la planta de e-Metanol a e-Gasolina (MtG por sus siglas en inglés), la cual estará compuesta por 2 unidades productoras, cada una equipada con un reactor para la conversión de e-Metanol a e-Gasolina, un fraccionador para la separación de la e-Gasolina liviana de la fracción pesada y una unidad de hidrotratamiento para cortar los hidrocarburos de cadena larga e hidrogenar los hidrocarburos insaturados. Tanto el e-Metanol como la e-Gasolina serán conducidos mediante tuberías hasta el Terminal de Cabo Negro para su exportación, en tanto el e-GL será transportado a través de tractocamiones hacia Puerto Mardones o el destino que corresponda. Objetivo El objetivo del Proyecto es la producción de e-Metanol, e-Gasolina y e-GL como combustible carbono neutral a partir de energía eólica, agua de mar, agua de proceso recirculada y captura de CO 2 del aire y/o fuentes biogénicas.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Modificación de Proyecto Continuidad Operacional Cerro Colorado mediante la incorporación de plataformas de prospección para sondajes mineros, estudios geotécnicos e hidrogeológicos y calicatas</t>
+          <t>Parque Eólico Faro del Sur</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2165082647</t>
+          <t>2160813317</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2165082647&amp;modo=ficha</t>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2160813317&amp;modo=ficha</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Primera</t>
+          <t>Duodécima</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>16/05/2025</t>
+          <t>22/12/2023</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -21987,17 +21982,17 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>Declaración de Impacto Ambiental</t>
+          <t>Estudio de Impacto Ambiental</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Prospecciones y exploraciones</t>
+          <t>Centrales generadoras de energía mayores a 3 MW</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Compañía Minera Cerro Colorado Ltda...</t>
+          <t>Eólica Faro del Sur S.P.A</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -22012,77 +22007,149 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>El presente Proyecto se localizará en las comunas de Pozo Almonte y Huara, Provincia del Tamarugal, y en la comuna de Alto Hospicio, Provincia de Iquique, todas pertenecientes a la Región de Tarapacá. Su objetivo principal corresponde a la ejecución de sondajes y calicatas, orientados a obtener la información necesaria y suficiente para reducir la incertidumbre geológica asociada al recurso minero, robustecer la caracterización de los niveles y calidad de los recursos hídricos subterráneos en el entorno de la faena minera Cerro Colorado y estudiar las propiedades físicas y mecánicas del suelo en áreas de interés para el desarrollo de futuros proyectos. Respecto de los sondajes se tiene que: el Proyecto contempla la ejecución de 201 sondajes, de los cuales 197 corresponden a sondajes terrestres y 4 corresponden a sondajes marinos, estos sondajes serán ejecutados en un total de 182 plataformas terrestres y 4 plataformas flotantes. Dichas plataformas se localizarán en tres sectores, que conforma el área del Proyecto: Sector Precordillera, Sector Pampa y Sector Costa. Los sondajes contemplados en el Proyecto se dividen en las siguientes categorías: Sondajes mineros: Incluyen un total de 97 sondajes destinados a reducir la incertidumbre geológica del cuerpo mineralizado y a establecer las bases para el desarrollo de futuros planes mineros. Sondajes hidrogeológicos: Comprenden 27 sondajes enfocados en recolectar información sobre los niveles y la calidad de los recursos hídricos subterráneos. Sondajes geotécnicos (terrestres): Se realizarán 73 sondajes con el propósito de analizar las propiedades físicas y mecánicas del suelo. Sondajes geotécnicos (marinos): Adicionalmente se contemplan 4 sondajes en el mar, orientados a analizar propiedades físicas y mecánicas del suelo marino. Respecto de las calicatas se tiene que: el Proyecto considera la ejecución de 81 calicatas, destinadas a describir la caracterización de las propiedades físicas y mecánicas del suelo. En este sentido, se indica que el Proyecto contempla habilitar un total de 70 áreas de trabajo para la ejecución de calicatas, de las cuales 60 se habilitarán en el Sector de Precordillera, 8 en Sector Pampa, y 2 en el Sector Costa. Tal como se considera para la ejecución de sondajes, algunas de las calicatas (11) serán ejecutadas en áreas de trabajo comunes, es decir, con otra calicata o con un sondaje. Objetivo El objetivo general del presente Proyecto corresponde a la ejecución de 197 sondajes terrestres y 4 sondajes marinos, y 81 calicatas, lo anterior con la finalidad de obtener información necesaria para el estudio y desarrollo de futuros proyectos de Cerro Colorado. En particular, el análisis de las muestras obtenidas, los estudios y las pruebas desarrolladas en los sondajes y/o calicatas, permitirán: · Reducir la incertidumbre geológica del cuerpo mineralizado. · Caracterizar los niveles y calidad de los recursos hídricos subterráneos en el entorno de la faena minera Cerro Colorado. · Determinar las propiedades físicas y mecánicas del suelo.</t>
+          <t>El Proyecto “Parque Eólico Faro del Sur” consiste en la construcción y operación de un parque eólico, en la comuna de Punta Arenas, Región de Magallanes y de la Antártica Chilena, con una potencia nominal de 384 MW y una vida útil proyectada de 29 años. El Parque Eólico está conformado por 64 aerogeneradores de tres palas, que se distribuirán en una superficie predial total de 3.791 hectáreas aproximadamente. Cada aerogenerador ocupará una superficie en promedio de 657,17 m2, tendrá una altura total de 200 m, y estará compuesto por una torre de 115 m de altura de buje y un rotor de 170 m de diámetro. El parque contará con una subestación elevadora de 33 kV a 66 kV en una superficie de 2,52 ha, donde se agruparán los circuitos internos y desde donde la energía será evacuada a través de una línea de transmisión de 66 kV, hasta una subestación reductora de 66 kV a 33 kV en una superficie de 0,45 ha. La Línea de Transmisión tendrá una longitud de aproximadamente 12,274 km y una superficie de 7,61 ha, la cual se extenderá de forma subterránea desde el Parque Eólico hasta el punto de entrega final en la Planta para la Producción de Combustibles Carbono Neutral (e-Combustibles) en el sector de Cabo Negro que se encuentra actualmente en evaluación. Adicionalmente, el Proyecto contará con instalaciones para la operación y seguridad del Parque Eólico tales como edificio de operación y mantenimiento, salas eléctricas, bodegas, oficinas, las que se emplazarán en el polígono destinado a la subestación elevadora. Objetivo El objetivo del Proyecto es la construcción y operación de un parque eólico de generación eléctrica de una potencia nominal de 384 MW, y la construcción y operación de una Línea de Transmisión de la energía producida, que permitirá aprovechar el recurso eólico de la Región de Magallanes y de la Antártica Chilena para generar energía limpia y sustentable.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Modificación de Proyecto Continuidad Operacional Cerro Colorado mediante la incorporación de plataformas de prospección para sondajes mineros, estudios geotécnicos e hidrogeológicos y calicatas</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2165082647</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2165082647&amp;modo=ficha</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Primera</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>60,000</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>16/05/2025</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Declaración de Impacto Ambiental</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Prospecciones y exploraciones</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Compañía Minera Cerro Colorado Ltda...</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Geobiota</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>Félix Hidalgo Reyes</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>El presente Proyecto se localizará en las comunas de Pozo Almonte y Huara, Provincia del Tamarugal, y en la comuna de Alto Hospicio, Provincia de Iquique, todas pertenecientes a la Región de Tarapacá. Su objetivo principal corresponde a la ejecución de sondajes y calicatas, orientados a obtener la información necesaria y suficiente para reducir la incertidumbre geológica asociada al recurso minero, robustecer la caracterización de los niveles y calidad de los recursos hídricos subterráneos en el entorno de la faena minera Cerro Colorado y estudiar las propiedades físicas y mecánicas del suelo en áreas de interés para el desarrollo de futuros proyectos. Respecto de los sondajes se tiene que: el Proyecto contempla la ejecución de 201 sondajes, de los cuales 197 corresponden a sondajes terrestres y 4 corresponden a sondajes marinos, estos sondajes serán ejecutados en un total de 182 plataformas terrestres y 4 plataformas flotantes. Dichas plataformas se localizarán en tres sectores, que conforma el área del Proyecto: Sector Precordillera, Sector Pampa y Sector Costa. Los sondajes contemplados en el Proyecto se dividen en las siguientes categorías: Sondajes mineros: Incluyen un total de 97 sondajes destinados a reducir la incertidumbre geológica del cuerpo mineralizado y a establecer las bases para el desarrollo de futuros planes mineros. Sondajes hidrogeológicos: Comprenden 27 sondajes enfocados en recolectar información sobre los niveles y la calidad de los recursos hídricos subterráneos. Sondajes geotécnicos (terrestres): Se realizarán 73 sondajes con el propósito de analizar las propiedades físicas y mecánicas del suelo. Sondajes geotécnicos (marinos): Adicionalmente se contemplan 4 sondajes en el mar, orientados a analizar propiedades físicas y mecánicas del suelo marino. Respecto de las calicatas se tiene que: el Proyecto considera la ejecución de 81 calicatas, destinadas a describir la caracterización de las propiedades físicas y mecánicas del suelo. En este sentido, se indica que el Proyecto contempla habilitar un total de 70 áreas de trabajo para la ejecución de calicatas, de las cuales 60 se habilitarán en el Sector de Precordillera, 8 en Sector Pampa, y 2 en el Sector Costa. Tal como se considera para la ejecución de sondajes, algunas de las calicatas (11) serán ejecutadas en áreas de trabajo comunes, es decir, con otra calicata o con un sondaje. Objetivo El objetivo general del presente Proyecto corresponde a la ejecución de 197 sondajes terrestres y 4 sondajes marinos, y 81 calicatas, lo anterior con la finalidad de obtener información necesaria para el estudio y desarrollo de futuros proyectos de Cerro Colorado. En particular, el análisis de las muestras obtenidas, los estudios y las pruebas desarrolladas en los sondajes y/o calicatas, permitirán: · Reducir la incertidumbre geológica del cuerpo mineralizado. · Caracterizar los niveles y calidad de los recursos hídricos subterráneos en el entorno de la faena minera Cerro Colorado. · Determinar las propiedades físicas y mecánicas del suelo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>Muro Portezuelo Llau-Llau</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
+      <c r="C310" t="inlineStr">
         <is>
           <t>2141908806</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr">
+      <c r="D310" t="inlineStr">
         <is>
           <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2141908806&amp;modo=ficha</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
+      <c r="E310" t="inlineStr">
         <is>
           <t>Cuarta</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
+      <c r="F310" t="inlineStr">
         <is>
           <t>23,000</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr">
+      <c r="G310" t="inlineStr">
         <is>
           <t>19/12/2018</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>Aprobado</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>Declaración de Impacto Ambiental</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Declaración de Impacto Ambiental</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
         <is>
           <t>Presas y embalses</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
+      <c r="K310" t="inlineStr">
         <is>
           <t>Minera Los Pelambres</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
+      <c r="L310" t="inlineStr">
         <is>
           <t>Geobiota</t>
         </is>
       </c>
-      <c r="M309" t="inlineStr">
+      <c r="M310" t="inlineStr">
         <is>
           <t>Félix Hidalgo Reyes</t>
         </is>
       </c>
-      <c r="N309" t="inlineStr">
+      <c r="N310" t="inlineStr">
         <is>
           <t>El Proyecto “Muro Portezuelo Llau-Llau” consiste en la construcción de un muro de contención con material de empréstito en el sector del portezuelo entre el valle de El Pupío y Llau Llau, cuya cota de coronamiento corresponderá a la cota 975 m.s.n.m, 8 metros más baja que la cota del muro principal del Tranque El Mauro (983 m.s.n.m). De acuerdo con el diseño y las características topográficas del emplazamiento del Tranque, si bien la cota del relave proyectado en dicho sector se ubica bajo la cota del portezuelo (964,5 y 966 respectivamente) se estima necesaria la construcción de este muro de contención que evitará el paso de aguas de proceso derivadas del Tranque hacia el Valle de Llau Llau. De acuerdo con ello, a través del Proyecto el Titular pretende implementar diversas obras y/o acciones que permitan garantizar el cumplimiento de lo comprometido. Dichas obras son las que se indican a continuación: Construcción de muro de contención en el sector del portezuelo entre el valle del Pupío y Llau Llau, de una altura de 21 metros (medida en el eje del coronamiento), que incluye la construcción de un cortafuga a los pies del muro compuesto por un cut off impermeable e inyecciones de lechada de cemento. Extracción de empréstitos y depósito de material excedente de excavación (Ambas actividades corresponden a acciones aprobadas en la RCA N °038/2004 para el sector de El Mauro ). Habilitación de Instalaciones de faena y caminos de acceso. Habilitación de instrumentación para monitorear el comportamiento del muro y aguas subterráneas. Objetivo El objetivo del Proyecto “Muro Portezuelo Llau-Llau” es la construcción de un muro de contención en el sector del portezuelo entre el valle de El Pupío y Llau Llau, cuya cota de coronamiento corresponderá a la cota 975 m.s.n.m, 8 metros más baja que la cota del muro principal del Tranque El Mauro (983 m.s.n.m), para evitar el paso de aguas de proceso derivadas del Tranque hacia el Valle de Llau Llau.</t>
         </is>

--- a/Experiencia SGA-GEOBIOTA.xlsx
+++ b/Experiencia SGA-GEOBIOTA.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaExperiencia" displayName="TablaExperiencia" ref="A1:N310" headerRowCount="1">
-  <autoFilter ref="A1:N310"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaExperiencia" displayName="TablaExperiencia" ref="A1:N311" headerRowCount="1">
+  <autoFilter ref="A1:N311"/>
   <tableColumns count="14">
     <tableColumn id="1" name="n"/>
     <tableColumn id="2" name="nombre_proyecto"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N310"/>
+  <dimension ref="A1:N311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -20488,12 +20488,12 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>En Admisión</t>
+          <t>En Calificación</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -22086,70 +22086,137 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Central de Almacenamiento de Energía Renovable por Bombeo Atacama</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2168909552</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2168909552&amp;modo=ficha</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Tercera</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>900,000</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>En Admisión</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Estudio de Impacto Ambiental</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Central Bombeo Atacama SpA</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Geobiota</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>fernanda camila vivallos alamos</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>El presente Proyecto se somete a evaluación ambiental a través de un Estudio de Impacto Ambiental (EIA), cuyo objetivo corresponde al almacenamiento y transporte de energía mediante la operación de una central de bombeo hidráulico de hasta 450 MW de potencia instalada y una capacidad de almacenamiento de hasta 3.600 megavatios hora (MWh) permitiendo una operación continua de generación de hasta 8 horas. Esta central se emplazará en la comuna de Caldera, provincia de Copiapó, región de Atacama. Cabe destacar que el Proyecto ingresa al Sistema de Evaluación de Impacto Ambiental (en adelante SEIA) mediante la tipología del artículo 3, letra a) del Reglamento del Sistema de Evaluación de Impacto Ambiental (RSEIA) D.S. Nº 40/12, incluyendo sus modificaciones y la Ley Nº 19.300/94 de Bases Generales del Medio Ambiente. En particular el Proyecto corresponde a la construcción y operación de una central de almacenamiento de energía renovable por bombeo hidráulico, cuyo sistema operará mediante el bombeo de agua desalinizada desde un embalse inferior (ubicado a aproximadamente 110 m.s.n.m.) hacia un embalse superior (ubicado a aproximadamente 425 m.s.n.m.), acumulando energía en forma de energía potencial, ambos embalses estarán conectados mediante un sistema de aducción e impulsión de agua desalinizada, que permite el traslado reversible del recurso hídrico. Cada embalse tendrá una capacidad aproximada de 4.800.000 de m 3 . La central anteriormente señalada se encontrará compuesta por el siguiente grupo de obras: Obras hidráulicas de almacenamiento : asociadas a los embalses superior e inferior. Obras de aducción e impulsión: sistema de tuberías de aducción e impulsión que conectan ambos embalses con un desnivel hidráulico tal que permita el flujo de agua por gravedad entre los mismos en periodo de alta demanda. Obras de generación : correspondiente a una casa de máquinas equipada con turbinas y sistemas de bombeo hidráulico. Obras de transmisión : correspondientes a una subestación elevadora y una línea de trasmisión eléctrica de 2x220 kV, de 151,3 m de longitud, para conectarse con la línea de transmisión existente LTE Suministro Cerro Negro Norte y Desalinizadora Pta. Totoralillo de 220 kV. El agua desalinizada que utilizará el sistema de almacenamiento energético provendrá de empresas de desalación actualmente operativas en la zona, las que cuentan con sus respectivas Resoluciones de Calificación Ambiental (RCA) e infraestructura autorizada para transporte, mediante las Tuberías de Suministro 1 y 2 de agua desalinizada. Objetivo El objetivo general del Proyecto consiste en implementar un sistema de almacenamiento de energía mediante el bombeo hidráulico reversible, que permita optimizar el uso de excedentes de energía eléctrica provenientes de fuentes renovables. Lo anterior se logrará a través de la construcción y operación de una central de bombeo hidráulico con una capacidad de hasta 450 MW. Con ello, se busca aportar flexibilidad operativa al Sistema Eléctrico Nacional (SEN), favoreciendo el aprovechamiento eficiente de la energía renovables y contribuyendo a la seguridad, estabilidad y sostenibilidad del suministro eléctrico del país</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B311" t="inlineStr">
         <is>
           <t>Muro Portezuelo Llau-Llau</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
+      <c r="C311" t="inlineStr">
         <is>
           <t>2141908806</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr">
+      <c r="D311" t="inlineStr">
         <is>
           <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2141908806&amp;modo=ficha</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
+      <c r="E311" t="inlineStr">
         <is>
           <t>Cuarta</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
+      <c r="F311" t="inlineStr">
         <is>
           <t>23,000</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
+      <c r="G311" t="inlineStr">
         <is>
           <t>19/12/2018</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>Aprobado</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>Declaración de Impacto Ambiental</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Declaración de Impacto Ambiental</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
         <is>
           <t>Presas y embalses</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
+      <c r="K311" t="inlineStr">
         <is>
           <t>Minera Los Pelambres</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
+      <c r="L311" t="inlineStr">
         <is>
           <t>Geobiota</t>
         </is>
       </c>
-      <c r="M310" t="inlineStr">
+      <c r="M311" t="inlineStr">
         <is>
           <t>Félix Hidalgo Reyes</t>
         </is>
       </c>
-      <c r="N310" t="inlineStr">
+      <c r="N311" t="inlineStr">
         <is>
           <t>El Proyecto “Muro Portezuelo Llau-Llau” consiste en la construcción de un muro de contención con material de empréstito en el sector del portezuelo entre el valle de El Pupío y Llau Llau, cuya cota de coronamiento corresponderá a la cota 975 m.s.n.m, 8 metros más baja que la cota del muro principal del Tranque El Mauro (983 m.s.n.m). De acuerdo con el diseño y las características topográficas del emplazamiento del Tranque, si bien la cota del relave proyectado en dicho sector se ubica bajo la cota del portezuelo (964,5 y 966 respectivamente) se estima necesaria la construcción de este muro de contención que evitará el paso de aguas de proceso derivadas del Tranque hacia el Valle de Llau Llau. De acuerdo con ello, a través del Proyecto el Titular pretende implementar diversas obras y/o acciones que permitan garantizar el cumplimiento de lo comprometido. Dichas obras son las que se indican a continuación: Construcción de muro de contención en el sector del portezuelo entre el valle del Pupío y Llau Llau, de una altura de 21 metros (medida en el eje del coronamiento), que incluye la construcción de un cortafuga a los pies del muro compuesto por un cut off impermeable e inyecciones de lechada de cemento. Extracción de empréstitos y depósito de material excedente de excavación (Ambas actividades corresponden a acciones aprobadas en la RCA N °038/2004 para el sector de El Mauro ). Habilitación de Instalaciones de faena y caminos de acceso. Habilitación de instrumentación para monitorear el comportamiento del muro y aguas subterráneas. Objetivo El objetivo del Proyecto “Muro Portezuelo Llau-Llau” es la construcción de un muro de contención en el sector del portezuelo entre el valle de El Pupío y Llau Llau, cuya cota de coronamiento corresponderá a la cota 975 m.s.n.m, 8 metros más baja que la cota del muro principal del Tranque El Mauro (983 m.s.n.m), para evitar el paso de aguas de proceso derivadas del Tranque hacia el Valle de Llau Llau.</t>
         </is>

--- a/Experiencia SGA-GEOBIOTA.xlsx
+++ b/Experiencia SGA-GEOBIOTA.xlsx
@@ -22116,12 +22116,12 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>En Admisión</t>
+          <t>En Calificación</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">

--- a/Experiencia SGA-GEOBIOTA.xlsx
+++ b/Experiencia SGA-GEOBIOTA.xlsx
@@ -20081,7 +20081,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>En Calificación</t>
+          <t>Aprobado</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>En Calificación</t>
+          <t>Aprobado</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">

--- a/Experiencia SGA-GEOBIOTA.xlsx
+++ b/Experiencia SGA-GEOBIOTA.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaExperiencia" displayName="TablaExperiencia" ref="A1:N311" headerRowCount="1">
-  <autoFilter ref="A1:N311"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaExperiencia" displayName="TablaExperiencia" ref="A1:N312" headerRowCount="1">
+  <autoFilter ref="A1:N312"/>
   <tableColumns count="14">
     <tableColumn id="1" name="n"/>
     <tableColumn id="2" name="nombre_proyecto"/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N311"/>
+  <dimension ref="A1:N312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -22153,70 +22153,142 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Nueva Línea 2x220 kV Gamboa-Chonchi</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2161109256</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2161109256&amp;modo=ficha</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Décima</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>26,431</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>24/01/2024</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>En Calificación</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Declaración de Impacto Ambiental</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Líneas de transmisión eléctrica de alto voltaje</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Sociedad Austral de Transmisión Troncal S.A.</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Geobiota</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>Ingrid Mariela Zelaya Lathan</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>A través de esta Declaración de Impacto Ambiental (DIA), se presenta el proyecto denominado "Nueva Línea 2X220 kV Gamboa-Chonchi", en adelante, el proyecto. Su objetivo principal es fortalecer el Sistema de Transmisión eléctrico de Chiloé, específicamente en la ciudad de Castro y sus alrededores, para garantizar un suministro continuo de energía para la población. El proyecto "Nueva Línea 2x220 kV Gamboa – Chonchi" consiste en la construcción y operación de una línea de transmisión eléctrica de 2x220 kV con una longitud de 24 km y 96 ha de faja (aproximadamente), que atraviesa las comunas de Castro y Chonchi, en la Región de Los Lagos. La línea se energizará inicialmente en 110 kV, con el tendido del primer circuito, y su capacidad será de al menos 90 MVA por circuito, de acuerdo con el Decreto Exento N°418/2017 del Ministerio de Energía. Una vez energizado en 110 kV, el primer circuito transportará una corriente de 472,4 Amperios. Posteriormente, se agregará un segundo circuito, y ambos serán energizados a 220 kV, lo que permitirá un transporte de corriente de 118,1 A por fase. En el marco del proyecto, se utilizarán caminos púbicos y los accesos existentes de predios particulares para facilitar el ingreso para la construcción de la nueva línea de transmisión eléctrica de 2x220 kV. Además, se establecerán patios de obra en ubicaciones estratégicas para optimizar la logística y el almacenamiento de materiales durante la construcción del proyecto. Estas medidas asegurarán una planificación adecuada y una implementación efectiva del proyecto de transmisión eléctrica. Los detalles específicos sobre el uso de accesos y la ubicación de los patios de obra se proporcionarán en los capítulos correspondientes de este documento. Objetivo El propósito fundamental de este proyecto es mejorar la calidad del servicio proporcionado a nuestros clientes en la Isla de Chiloé, logrando un aumento en la capacidad de transporte de energía y mejorar la calidad operacional al permitir reducir las pérdidas por fallas, al acotarlas y aislarlas a sectores específicos dentro de Chiloé que se vieran afectados, sin impactar a la continuidad del servicio del resto de la Isla de Chiloé. Asimismo, la infraestructura propuesta ofrece una mayor estabilidad y flexibilidad al sistema que actualmente abastece a una parte significativa de la Isla de Chiloé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>Muro Portezuelo Llau-Llau</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
+      <c r="C312" t="inlineStr">
         <is>
           <t>2141908806</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr">
+      <c r="D312" t="inlineStr">
         <is>
           <t>https://seia.sea.gob.cl/expediente/expediente.php?id_expediente=2141908806&amp;modo=ficha</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
+      <c r="E312" t="inlineStr">
         <is>
           <t>Cuarta</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr">
+      <c r="F312" t="inlineStr">
         <is>
           <t>23,000</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
+      <c r="G312" t="inlineStr">
         <is>
           <t>19/12/2018</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>Aprobado</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>Declaración de Impacto Ambiental</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr">
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Aprobado</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Declaración de Impacto Ambiental</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
         <is>
           <t>Presas y embalses</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
+      <c r="K312" t="inlineStr">
         <is>
           <t>Minera Los Pelambres</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
+      <c r="L312" t="inlineStr">
         <is>
           <t>Geobiota</t>
         </is>
       </c>
-      <c r="M311" t="inlineStr">
+      <c r="M312" t="inlineStr">
         <is>
           <t>Félix Hidalgo Reyes</t>
         </is>
       </c>
-      <c r="N311" t="inlineStr">
+      <c r="N312" t="inlineStr">
         <is>
           <t>El Proyecto “Muro Portezuelo Llau-Llau” consiste en la construcción de un muro de contención con material de empréstito en el sector del portezuelo entre el valle de El Pupío y Llau Llau, cuya cota de coronamiento corresponderá a la cota 975 m.s.n.m, 8 metros más baja que la cota del muro principal del Tranque El Mauro (983 m.s.n.m). De acuerdo con el diseño y las características topográficas del emplazamiento del Tranque, si bien la cota del relave proyectado en dicho sector se ubica bajo la cota del portezuelo (964,5 y 966 respectivamente) se estima necesaria la construcción de este muro de contención que evitará el paso de aguas de proceso derivadas del Tranque hacia el Valle de Llau Llau. De acuerdo con ello, a través del Proyecto el Titular pretende implementar diversas obras y/o acciones que permitan garantizar el cumplimiento de lo comprometido. Dichas obras son las que se indican a continuación: Construcción de muro de contención en el sector del portezuelo entre el valle del Pupío y Llau Llau, de una altura de 21 metros (medida en el eje del coronamiento), que incluye la construcción de un cortafuga a los pies del muro compuesto por un cut off impermeable e inyecciones de lechada de cemento. Extracción de empréstitos y depósito de material excedente de excavación (Ambas actividades corresponden a acciones aprobadas en la RCA N °038/2004 para el sector de El Mauro ). Habilitación de Instalaciones de faena y caminos de acceso. Habilitación de instrumentación para monitorear el comportamiento del muro y aguas subterráneas. Objetivo El objetivo del Proyecto “Muro Portezuelo Llau-Llau” es la construcción de un muro de contención en el sector del portezuelo entre el valle de El Pupío y Llau Llau, cuya cota de coronamiento corresponderá a la cota 975 m.s.n.m, 8 metros más baja que la cota del muro principal del Tranque El Mauro (983 m.s.n.m), para evitar el paso de aguas de proceso derivadas del Tranque hacia el Valle de Llau Llau.</t>
         </is>

--- a/Experiencia SGA-GEOBIOTA.xlsx
+++ b/Experiencia SGA-GEOBIOTA.xlsx
@@ -14721,7 +14721,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>GM Energy SpA</t>
+          <t>El Campesino SPA</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">

--- a/Experiencia SGA-GEOBIOTA.xlsx
+++ b/Experiencia SGA-GEOBIOTA.xlsx
@@ -18316,7 +18316,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Compañía Minera Lomas Bayas</t>
+          <t>Compañía Minera Lomas Bayas.</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>En Calificación</t>
+          <t>Aprobado</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Compañía Minera Lomas Bayas</t>
+          <t>Compañía Minera Lomas Bayas.</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">

--- a/Experiencia SGA-GEOBIOTA.xlsx
+++ b/Experiencia SGA-GEOBIOTA.xlsx
@@ -19731,7 +19731,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>En Calificación</t>
+          <t>Aprobado</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
